--- a/amc_book/ICICI Prudential Mutual Fund/ICICI Pru Large Cap Fund _G_/FACT_SHEET_2026-06-25.xlsx
+++ b/amc_book/ICICI Prudential Mutual Fund/ICICI Pru Large Cap Fund _G_/FACT_SHEET_2026-06-25.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O89"/>
+  <dimension ref="A1:O92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -618,25 +618,25 @@
         </is>
       </c>
       <c r="F6" s="6" t="n">
-        <v>2765595</v>
+        <v>2642495</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>4368.7</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>1208.2055</v>
+        <v>1154.4268</v>
       </c>
       <c r="I6" s="7" t="n">
         <v>4368.7</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>1208.2055</v>
+        <v>1154.4268</v>
       </c>
       <c r="K6" s="7" t="n">
         <v>4368.9</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>1208.2608</v>
+        <v>1154.4796</v>
       </c>
       <c r="M6" s="9" t="n">
         <v>-0.0046</v>
@@ -645,7 +645,7 @@
         <v>-6.999999999999999e-05</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>1.5836</v>
+        <v>1.5131</v>
       </c>
     </row>
     <row r="7">
@@ -663,14 +663,14 @@
       <c r="H7" s="11" t="n"/>
       <c r="I7" s="11" t="n"/>
       <c r="J7" s="13" t="n">
-        <v>1208.206</v>
+        <v>1154.427</v>
       </c>
       <c r="K7" s="11" t="n"/>
       <c r="L7" s="11" t="n"/>
       <c r="M7" s="11" t="n"/>
       <c r="N7" s="11" t="n"/>
       <c r="O7" s="14" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="8">
@@ -679,122 +679,92 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>INE917I01010</t>
+          <t>INE1TAE01010</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Bajaj Auto Ltd.</t>
+          <t>Tata Motors Ltd.</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Automobiles</t>
+          <t>Agricultural, Commercial &amp; Construction Vehicles</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>tactical</t>
+          <t>cyclical</t>
         </is>
       </c>
       <c r="F8" s="6" t="n">
-        <v>1922275</v>
+        <v>26173401</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>9843</v>
+        <v>431.9</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>1892.0953</v>
+        <v>1130.4292</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>9843</v>
+        <v>431.9</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>1892.0953</v>
+        <v>1130.4292</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>9750</v>
+        <v>411.4</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>1874.2181</v>
+        <v>1076.7737</v>
       </c>
       <c r="M8" s="9" t="n">
-        <v>0.9538</v>
+        <v>4.983</v>
       </c>
       <c r="N8" s="10" t="n">
-        <v>0.02365</v>
+        <v>0.07383000000000001</v>
       </c>
       <c r="O8" s="9" t="n">
-        <v>2.4799</v>
+        <v>1.4816</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>INE066A01021</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Eicher Motors Ltd.</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Automobiles</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>structural</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>2130218</v>
-      </c>
-      <c r="G9" s="7" t="n">
-        <v>7598</v>
-      </c>
-      <c r="H9" s="8" t="n">
-        <v>1618.5396</v>
-      </c>
-      <c r="I9" s="7" t="n">
-        <v>7598</v>
-      </c>
-      <c r="J9" s="8" t="n">
-        <v>1618.5396</v>
-      </c>
-      <c r="K9" s="7" t="n">
-        <v>7572</v>
-      </c>
-      <c r="L9" s="8" t="n">
-        <v>1613.0011</v>
-      </c>
-      <c r="M9" s="9" t="n">
-        <v>0.3434</v>
-      </c>
-      <c r="N9" s="10" t="n">
-        <v>0.00728</v>
-      </c>
-      <c r="O9" s="9" t="n">
-        <v>2.1214</v>
+      <c r="A9" s="11" t="n"/>
+      <c r="B9" s="11" t="n"/>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Agricultural, Commercial &amp; Construction Vehicles — subtotal</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="n"/>
+      <c r="E9" s="11" t="n"/>
+      <c r="F9" s="11" t="n"/>
+      <c r="G9" s="11" t="n"/>
+      <c r="H9" s="11" t="n"/>
+      <c r="I9" s="11" t="n"/>
+      <c r="J9" s="13" t="n">
+        <v>1130.429</v>
+      </c>
+      <c r="K9" s="11" t="n"/>
+      <c r="L9" s="11" t="n"/>
+      <c r="M9" s="11" t="n"/>
+      <c r="N9" s="11" t="n"/>
+      <c r="O9" s="14" t="n">
+        <v>1.48</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>INE494B01023</t>
+          <t>INE917I01010</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>TVS Motor Company Ltd.</t>
+          <t>Bajaj Auto Ltd.</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -804,52 +774,52 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>structural</t>
+          <t>tactical</t>
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>4214802</v>
+        <v>1838957</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>3569.7</v>
+        <v>9843</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>1504.5579</v>
+        <v>1810.0854</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>3569.7</v>
+        <v>9843</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>1504.5579</v>
+        <v>1810.0854</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>3440.6</v>
+        <v>9750</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>1450.1448</v>
+        <v>1792.9831</v>
       </c>
       <c r="M10" s="9" t="n">
-        <v>3.7523</v>
+        <v>0.9538</v>
       </c>
       <c r="N10" s="10" t="n">
-        <v>0.074</v>
+        <v>0.02263</v>
       </c>
       <c r="O10" s="9" t="n">
-        <v>1.972</v>
+        <v>2.3724</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>INE101A01026</t>
+          <t>INE155A01022</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Mahindra &amp; Mahindra Ltd.</t>
+          <t>Tata Motors Passenger Vehicles Ltd.</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -859,52 +829,52 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>structural</t>
+          <t>cyclical</t>
         </is>
       </c>
       <c r="F11" s="6" t="n">
-        <v>4011673</v>
+        <v>41084470</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>3182.2</v>
+        <v>353.2</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>1276.5946</v>
+        <v>1451.1035</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>3182.2</v>
+        <v>353.2</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>1276.5946</v>
+        <v>1451.1035</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>3064.5</v>
+        <v>349.7</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>1229.3772</v>
+        <v>1436.7239</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>3.8408</v>
+        <v>1.0009</v>
       </c>
       <c r="N11" s="10" t="n">
-        <v>0.06426</v>
+        <v>0.01904</v>
       </c>
       <c r="O11" s="9" t="n">
-        <v>1.6732</v>
+        <v>1.9019</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>INE0V6F01027</t>
+          <t>INE066A01021</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Hyundai Motor India Ltd.</t>
+          <t>Eicher Motors Ltd.</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -918,183 +888,183 @@
         </is>
       </c>
       <c r="F12" s="6" t="n">
-        <v>4977365</v>
+        <v>1839961</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>1969.4</v>
+        <v>7598</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>980.2423</v>
+        <v>1398.0024</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>1969.4</v>
+        <v>7598</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>980.2423</v>
+        <v>1398.0024</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>1942.2</v>
+        <v>7572</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>966.7038</v>
+        <v>1393.2185</v>
       </c>
       <c r="M12" s="9" t="n">
-        <v>1.4005</v>
+        <v>0.3434</v>
       </c>
       <c r="N12" s="10" t="n">
-        <v>0.01799</v>
+        <v>0.00629</v>
       </c>
       <c r="O12" s="9" t="n">
-        <v>1.2848</v>
+        <v>1.8323</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>INE494B01023</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>TVS Motor Company Ltd.</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Automobiles</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>3662812</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>3569.7</v>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>1307.514</v>
+      </c>
+      <c r="I13" s="7" t="n">
+        <v>3569.7</v>
+      </c>
+      <c r="J13" s="8" t="n">
+        <v>1307.514</v>
+      </c>
+      <c r="K13" s="7" t="n">
+        <v>3440.6</v>
+      </c>
+      <c r="L13" s="8" t="n">
+        <v>1260.2271</v>
+      </c>
+      <c r="M13" s="9" t="n">
+        <v>3.7523</v>
+      </c>
+      <c r="N13" s="10" t="n">
+        <v>0.0643</v>
+      </c>
+      <c r="O13" s="9" t="n">
+        <v>1.7137</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>INE158A01026</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Hero Motocorp Ltd.</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>INE101A01026</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Mahindra &amp; Mahindra Ltd.</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Automobiles</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>structural</t>
         </is>
       </c>
-      <c r="F13" s="6" t="n">
-        <v>1908968</v>
-      </c>
-      <c r="G13" s="7" t="n">
-        <v>4896.1</v>
-      </c>
-      <c r="H13" s="8" t="n">
-        <v>934.6498</v>
-      </c>
-      <c r="I13" s="7" t="n">
-        <v>4896.1</v>
-      </c>
-      <c r="J13" s="8" t="n">
-        <v>934.6498</v>
-      </c>
-      <c r="K13" s="7" t="n">
-        <v>4897.2</v>
-      </c>
-      <c r="L13" s="8" t="n">
-        <v>934.8598</v>
-      </c>
-      <c r="M13" s="9" t="n">
-        <v>-0.0225</v>
-      </c>
-      <c r="N13" s="10" t="n">
-        <v>-0.00028</v>
-      </c>
-      <c r="O13" s="9" t="n">
-        <v>1.225</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="n"/>
-      <c r="B14" s="11" t="n"/>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="F14" s="6" t="n">
+        <v>3237216</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>3182.2</v>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>1030.1469</v>
+      </c>
+      <c r="I14" s="7" t="n">
+        <v>3182.2</v>
+      </c>
+      <c r="J14" s="8" t="n">
+        <v>1030.1469</v>
+      </c>
+      <c r="K14" s="7" t="n">
+        <v>3064.5</v>
+      </c>
+      <c r="L14" s="8" t="n">
+        <v>992.0448</v>
+      </c>
+      <c r="M14" s="9" t="n">
+        <v>3.8408</v>
+      </c>
+      <c r="N14" s="10" t="n">
+        <v>0.05186</v>
+      </c>
+      <c r="O14" s="9" t="n">
+        <v>1.3502</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="n"/>
+      <c r="B15" s="11" t="n"/>
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>Automobiles — subtotal</t>
         </is>
       </c>
-      <c r="D14" s="11" t="n"/>
-      <c r="E14" s="11" t="n"/>
-      <c r="F14" s="11" t="n"/>
-      <c r="G14" s="11" t="n"/>
-      <c r="H14" s="11" t="n"/>
-      <c r="I14" s="11" t="n"/>
-      <c r="J14" s="13" t="n">
-        <v>8206.679</v>
-      </c>
-      <c r="K14" s="11" t="n"/>
-      <c r="L14" s="11" t="n"/>
-      <c r="M14" s="11" t="n"/>
-      <c r="N14" s="11" t="n"/>
-      <c r="O14" s="14" t="n">
-        <v>10.76</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>INE238A01034</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Axis Bank Ltd.</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>Banks</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>structural</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>10262653</v>
-      </c>
-      <c r="G15" s="7" t="n">
-        <v>1377.2</v>
-      </c>
-      <c r="H15" s="8" t="n">
-        <v>1413.3726</v>
-      </c>
-      <c r="I15" s="7" t="n">
-        <v>1377.2</v>
-      </c>
-      <c r="J15" s="8" t="n">
-        <v>1413.3726</v>
-      </c>
-      <c r="K15" s="7" t="n">
-        <v>1384.5</v>
-      </c>
-      <c r="L15" s="8" t="n">
-        <v>1420.8643</v>
-      </c>
-      <c r="M15" s="9" t="n">
-        <v>-0.5273</v>
-      </c>
-      <c r="N15" s="10" t="n">
-        <v>-0.009769999999999999</v>
-      </c>
-      <c r="O15" s="9" t="n">
-        <v>1.8525</v>
+      <c r="D15" s="11" t="n"/>
+      <c r="E15" s="11" t="n"/>
+      <c r="F15" s="11" t="n"/>
+      <c r="G15" s="11" t="n"/>
+      <c r="H15" s="11" t="n"/>
+      <c r="I15" s="11" t="n"/>
+      <c r="J15" s="13" t="n">
+        <v>6996.852</v>
+      </c>
+      <c r="K15" s="11" t="n"/>
+      <c r="L15" s="11" t="n"/>
+      <c r="M15" s="11" t="n"/>
+      <c r="N15" s="11" t="n"/>
+      <c r="O15" s="14" t="n">
+        <v>9.17</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>INE090A01021</t>
+          <t>INE238A01034</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>ICICI Bank Ltd.</t>
+          <t>Axis Bank Ltd.</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -1108,48 +1078,48 @@
         </is>
       </c>
       <c r="F16" s="6" t="n">
-        <v>10022171</v>
+        <v>10551330</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>1387.5</v>
+        <v>1377.2</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>1390.5762</v>
+        <v>1453.1292</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>1387.5</v>
+        <v>1377.2</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>1390.5762</v>
+        <v>1453.1292</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>1373.6</v>
+        <v>1384.5</v>
       </c>
       <c r="L16" s="8" t="n">
-        <v>1376.6454</v>
+        <v>1460.8316</v>
       </c>
       <c r="M16" s="9" t="n">
-        <v>1.0119</v>
+        <v>-0.5273</v>
       </c>
       <c r="N16" s="10" t="n">
-        <v>0.01844</v>
+        <v>-0.01004</v>
       </c>
       <c r="O16" s="9" t="n">
-        <v>1.8226</v>
+        <v>1.9046</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>INE237A01036</t>
+          <t>INE062A01020</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Kotak Mahindra Bank Ltd.</t>
+          <t>State Bank Of India</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -1163,48 +1133,48 @@
         </is>
       </c>
       <c r="F17" s="6" t="n">
-        <v>32327316</v>
+        <v>12151217</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>409</v>
+        <v>1045.4</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>1322.1872</v>
+        <v>1270.2882</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>409</v>
+        <v>1045.4</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>1322.1872</v>
+        <v>1270.2882</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>405.95</v>
+        <v>1034.6</v>
       </c>
       <c r="L17" s="8" t="n">
-        <v>1312.3274</v>
+        <v>1257.1649</v>
       </c>
       <c r="M17" s="9" t="n">
-        <v>0.7513</v>
+        <v>1.0439</v>
       </c>
       <c r="N17" s="10" t="n">
-        <v>0.01302</v>
+        <v>0.01738</v>
       </c>
       <c r="O17" s="9" t="n">
-        <v>1.7329</v>
+        <v>1.6649</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>INE040A01034</t>
+          <t>INE090A01021</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>HDFC Bank Ltd.</t>
+          <t>ICICI Bank Ltd.</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -1218,48 +1188,48 @@
         </is>
       </c>
       <c r="F18" s="6" t="n">
-        <v>13168796</v>
+        <v>9080087</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>796.3</v>
+        <v>1387.5</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>1048.6312</v>
+        <v>1259.8621</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>796.3</v>
+        <v>1387.5</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>1048.6312</v>
+        <v>1259.8621</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>793.2</v>
+        <v>1373.6</v>
       </c>
       <c r="L18" s="8" t="n">
-        <v>1044.5489</v>
+        <v>1247.2408</v>
       </c>
       <c r="M18" s="9" t="n">
-        <v>0.3908</v>
+        <v>1.0119</v>
       </c>
       <c r="N18" s="10" t="n">
-        <v>0.00537</v>
+        <v>0.01671</v>
       </c>
       <c r="O18" s="9" t="n">
-        <v>1.3744</v>
+        <v>1.6513</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>INE062A01020</t>
+          <t>INE237A01036</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>State Bank Of India</t>
+          <t>Kotak Mahindra Bank Ltd.</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -1273,34 +1243,34 @@
         </is>
       </c>
       <c r="F19" s="6" t="n">
-        <v>9376719</v>
+        <v>30310617</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>1045.4</v>
+        <v>409</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>980.2422</v>
+        <v>1239.7042</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>1045.4</v>
+        <v>409</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>980.2422</v>
+        <v>1239.7042</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>1034.6</v>
+        <v>405.95</v>
       </c>
       <c r="L19" s="8" t="n">
-        <v>970.1153</v>
+        <v>1230.4595</v>
       </c>
       <c r="M19" s="9" t="n">
-        <v>1.0439</v>
+        <v>0.7513</v>
       </c>
       <c r="N19" s="10" t="n">
-        <v>0.01341</v>
+        <v>0.01221</v>
       </c>
       <c r="O19" s="9" t="n">
-        <v>1.2848</v>
+        <v>1.6248</v>
       </c>
     </row>
     <row r="20">
@@ -1318,609 +1288,579 @@
       <c r="H20" s="11" t="n"/>
       <c r="I20" s="11" t="n"/>
       <c r="J20" s="13" t="n">
-        <v>6155.009</v>
+        <v>5222.984</v>
       </c>
       <c r="K20" s="11" t="n"/>
       <c r="L20" s="11" t="n"/>
       <c r="M20" s="11" t="n"/>
       <c r="N20" s="11" t="n"/>
       <c r="O20" s="14" t="n">
-        <v>8.07</v>
+        <v>6.85</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>INE127D01025</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>HDFC Asset Management Company Ltd.</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Capital Markets</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>cyclical</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>4016586</v>
+      </c>
+      <c r="G21" s="7" t="n">
+        <v>2649.7</v>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>1064.2748</v>
+      </c>
+      <c r="I21" s="7" t="n">
+        <v>2649.7</v>
+      </c>
+      <c r="J21" s="8" t="n">
+        <v>1064.2748</v>
+      </c>
+      <c r="K21" s="7" t="n">
+        <v>2625.1</v>
+      </c>
+      <c r="L21" s="8" t="n">
+        <v>1054.394</v>
+      </c>
+      <c r="M21" s="9" t="n">
+        <v>0.9371</v>
+      </c>
+      <c r="N21" s="10" t="n">
+        <v>0.01307</v>
+      </c>
+      <c r="O21" s="9" t="n">
+        <v>1.3949</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="n"/>
+      <c r="B22" s="11" t="n"/>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>Capital Markets — subtotal</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="n"/>
+      <c r="E22" s="11" t="n"/>
+      <c r="F22" s="11" t="n"/>
+      <c r="G22" s="11" t="n"/>
+      <c r="H22" s="11" t="n"/>
+      <c r="I22" s="11" t="n"/>
+      <c r="J22" s="13" t="n">
+        <v>1064.275</v>
+      </c>
+      <c r="K22" s="11" t="n"/>
+      <c r="L22" s="11" t="n"/>
+      <c r="M22" s="11" t="n"/>
+      <c r="N22" s="11" t="n"/>
+      <c r="O22" s="14" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>INE047A01021</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>Grasim Industries Ltd.</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>Cement &amp; Cement Products</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>tactical</t>
         </is>
       </c>
-      <c r="F21" s="6" t="n">
-        <v>7145271</v>
-      </c>
-      <c r="G21" s="7" t="n">
+      <c r="F23" s="6" t="n">
+        <v>6252611</v>
+      </c>
+      <c r="G23" s="7" t="n">
         <v>3126.6</v>
       </c>
-      <c r="H21" s="8" t="n">
-        <v>2234.0404</v>
-      </c>
-      <c r="I21" s="7" t="n">
+      <c r="H23" s="8" t="n">
+        <v>1954.9414</v>
+      </c>
+      <c r="I23" s="7" t="n">
         <v>3126.6</v>
       </c>
-      <c r="J21" s="8" t="n">
-        <v>2234.0404</v>
-      </c>
-      <c r="K21" s="7" t="n">
+      <c r="J23" s="8" t="n">
+        <v>1954.9414</v>
+      </c>
+      <c r="K23" s="7" t="n">
         <v>3127.9</v>
       </c>
-      <c r="L21" s="8" t="n">
-        <v>2234.9693</v>
-      </c>
-      <c r="M21" s="9" t="n">
+      <c r="L23" s="8" t="n">
+        <v>1955.7542</v>
+      </c>
+      <c r="M23" s="9" t="n">
         <v>-0.0416</v>
       </c>
-      <c r="N21" s="10" t="n">
-        <v>-0.00122</v>
-      </c>
-      <c r="O21" s="9" t="n">
-        <v>2.9281</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>INE070A01015</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>Shree Cements Ltd.</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>Cement &amp; Cement Products</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>structural</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>442905</v>
-      </c>
-      <c r="G22" s="7" t="n">
-        <v>25735</v>
-      </c>
-      <c r="H22" s="8" t="n">
-        <v>1139.816</v>
-      </c>
-      <c r="I22" s="7" t="n">
-        <v>25735</v>
-      </c>
-      <c r="J22" s="8" t="n">
-        <v>1139.816</v>
-      </c>
-      <c r="K22" s="7" t="n">
-        <v>26070</v>
-      </c>
-      <c r="L22" s="8" t="n">
-        <v>1154.6533</v>
-      </c>
-      <c r="M22" s="9" t="n">
-        <v>-1.285</v>
-      </c>
-      <c r="N22" s="10" t="n">
-        <v>-0.0192</v>
-      </c>
-      <c r="O22" s="9" t="n">
-        <v>1.4939</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="11" t="n"/>
-      <c r="B23" s="11" t="n"/>
-      <c r="C23" s="12" t="inlineStr">
-        <is>
-          <t>Cement &amp; Cement Products — subtotal</t>
-        </is>
-      </c>
-      <c r="D23" s="11" t="n"/>
-      <c r="E23" s="11" t="n"/>
-      <c r="F23" s="11" t="n"/>
-      <c r="G23" s="11" t="n"/>
-      <c r="H23" s="11" t="n"/>
-      <c r="I23" s="11" t="n"/>
-      <c r="J23" s="13" t="n">
-        <v>3373.856</v>
-      </c>
-      <c r="K23" s="11" t="n"/>
-      <c r="L23" s="11" t="n"/>
-      <c r="M23" s="11" t="n"/>
-      <c r="N23" s="11" t="n"/>
-      <c r="O23" s="14" t="n">
-        <v>4.42</v>
+      <c r="N23" s="10" t="n">
+        <v>-0.00107</v>
+      </c>
+      <c r="O23" s="9" t="n">
+        <v>2.5623</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>INE070A01015</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Shree Cements Ltd.</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Cement &amp; Cement Products</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>428918</v>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>25735</v>
+      </c>
+      <c r="H24" s="8" t="n">
+        <v>1103.8205</v>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>25735</v>
+      </c>
+      <c r="J24" s="8" t="n">
+        <v>1103.8205</v>
+      </c>
+      <c r="K24" s="7" t="n">
+        <v>26070</v>
+      </c>
+      <c r="L24" s="8" t="n">
+        <v>1118.1892</v>
+      </c>
+      <c r="M24" s="9" t="n">
+        <v>-1.285</v>
+      </c>
+      <c r="N24" s="10" t="n">
+        <v>-0.01859</v>
+      </c>
+      <c r="O24" s="9" t="n">
+        <v>1.4467</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="n"/>
+      <c r="B25" s="11" t="n"/>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>Cement &amp; Cement Products — subtotal</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="n"/>
+      <c r="E25" s="11" t="n"/>
+      <c r="F25" s="11" t="n"/>
+      <c r="G25" s="11" t="n"/>
+      <c r="H25" s="11" t="n"/>
+      <c r="I25" s="11" t="n"/>
+      <c r="J25" s="13" t="n">
+        <v>3058.762</v>
+      </c>
+      <c r="K25" s="11" t="n"/>
+      <c r="L25" s="11" t="n"/>
+      <c r="M25" s="11" t="n"/>
+      <c r="N25" s="11" t="n"/>
+      <c r="O25" s="14" t="n">
+        <v>4.01</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>INE021A01026</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>Asian Paints Ltd.</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>Consumer Durables</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>tactical</t>
         </is>
       </c>
-      <c r="F24" s="6" t="n">
-        <v>8445639</v>
-      </c>
-      <c r="G24" s="7" t="n">
+      <c r="F26" s="6" t="n">
+        <v>5632712</v>
+      </c>
+      <c r="G26" s="7" t="n">
         <v>2645.2</v>
       </c>
-      <c r="H24" s="8" t="n">
-        <v>2234.0404</v>
-      </c>
-      <c r="I24" s="7" t="n">
+      <c r="H26" s="8" t="n">
+        <v>1489.965</v>
+      </c>
+      <c r="I26" s="7" t="n">
         <v>2645.2</v>
       </c>
-      <c r="J24" s="8" t="n">
-        <v>2234.0404</v>
-      </c>
-      <c r="K24" s="7" t="n">
+      <c r="J26" s="8" t="n">
+        <v>1489.965</v>
+      </c>
+      <c r="K26" s="7" t="n">
         <v>2667.5</v>
       </c>
-      <c r="L24" s="8" t="n">
-        <v>2252.8742</v>
-      </c>
-      <c r="M24" s="9" t="n">
+      <c r="L26" s="8" t="n">
+        <v>1502.5259</v>
+      </c>
+      <c r="M26" s="9" t="n">
         <v>-0.836</v>
       </c>
-      <c r="N24" s="10" t="n">
-        <v>-0.02448</v>
-      </c>
-      <c r="O24" s="9" t="n">
-        <v>2.9281</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>INE280A01028</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>Titan Company Ltd.</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Consumer Durables</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>structural</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="n">
-        <v>3346699</v>
-      </c>
-      <c r="G25" s="7" t="n">
-        <v>4291.3</v>
-      </c>
-      <c r="H25" s="8" t="n">
-        <v>1436.1689</v>
-      </c>
-      <c r="I25" s="7" t="n">
-        <v>4291.3</v>
-      </c>
-      <c r="J25" s="8" t="n">
-        <v>1436.1689</v>
-      </c>
-      <c r="K25" s="7" t="n">
-        <v>4323.8</v>
-      </c>
-      <c r="L25" s="8" t="n">
-        <v>1447.0457</v>
-      </c>
-      <c r="M25" s="9" t="n">
-        <v>-0.7517</v>
-      </c>
-      <c r="N25" s="10" t="n">
-        <v>-0.01415</v>
-      </c>
-      <c r="O25" s="9" t="n">
-        <v>1.8823</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="11" t="n"/>
-      <c r="B26" s="11" t="n"/>
-      <c r="C26" s="12" t="inlineStr">
-        <is>
-          <t>Consumer Durables — subtotal</t>
-        </is>
-      </c>
-      <c r="D26" s="11" t="n"/>
-      <c r="E26" s="11" t="n"/>
-      <c r="F26" s="11" t="n"/>
-      <c r="G26" s="11" t="n"/>
-      <c r="H26" s="11" t="n"/>
-      <c r="I26" s="11" t="n"/>
-      <c r="J26" s="13" t="n">
-        <v>3670.209</v>
-      </c>
-      <c r="K26" s="11" t="n"/>
-      <c r="L26" s="11" t="n"/>
-      <c r="M26" s="11" t="n"/>
-      <c r="N26" s="11" t="n"/>
-      <c r="O26" s="14" t="n">
-        <v>4.81</v>
+      <c r="N26" s="10" t="n">
+        <v>-0.01633</v>
+      </c>
+      <c r="O26" s="9" t="n">
+        <v>1.9528</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>INE280A01028</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Titan Company Ltd.</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>3199548</v>
+      </c>
+      <c r="G27" s="7" t="n">
+        <v>4291.3</v>
+      </c>
+      <c r="H27" s="8" t="n">
+        <v>1373.022</v>
+      </c>
+      <c r="I27" s="7" t="n">
+        <v>4291.3</v>
+      </c>
+      <c r="J27" s="8" t="n">
+        <v>1373.022</v>
+      </c>
+      <c r="K27" s="7" t="n">
+        <v>4323.8</v>
+      </c>
+      <c r="L27" s="8" t="n">
+        <v>1383.4206</v>
+      </c>
+      <c r="M27" s="9" t="n">
+        <v>-0.7517</v>
+      </c>
+      <c r="N27" s="10" t="n">
+        <v>-0.01353</v>
+      </c>
+      <c r="O27" s="9" t="n">
+        <v>1.7996</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="n"/>
+      <c r="B28" s="11" t="n"/>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>Consumer Durables — subtotal</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="n"/>
+      <c r="E28" s="11" t="n"/>
+      <c r="F28" s="11" t="n"/>
+      <c r="G28" s="11" t="n"/>
+      <c r="H28" s="11" t="n"/>
+      <c r="I28" s="11" t="n"/>
+      <c r="J28" s="13" t="n">
+        <v>2862.987</v>
+      </c>
+      <c r="K28" s="11" t="n"/>
+      <c r="L28" s="11" t="n"/>
+      <c r="M28" s="11" t="n"/>
+      <c r="N28" s="11" t="n"/>
+      <c r="O28" s="14" t="n">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>INE154A01025</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>ITC Ltd.</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>INE030A01027</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Hindustan Unilever Ltd.</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>Diversified Fmcg</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>structural</t>
         </is>
       </c>
-      <c r="F27" s="6" t="n">
-        <v>40876180</v>
-      </c>
-      <c r="G27" s="7" t="n">
-        <v>290</v>
-      </c>
-      <c r="H27" s="8" t="n">
-        <v>1185.4092</v>
-      </c>
-      <c r="I27" s="7" t="n">
-        <v>290</v>
-      </c>
-      <c r="J27" s="8" t="n">
-        <v>1185.4092</v>
-      </c>
-      <c r="K27" s="7" t="n">
-        <v>290.35</v>
-      </c>
-      <c r="L27" s="8" t="n">
-        <v>1186.8399</v>
-      </c>
-      <c r="M27" s="9" t="n">
-        <v>-0.1205</v>
-      </c>
-      <c r="N27" s="10" t="n">
-        <v>-0.00187</v>
-      </c>
-      <c r="O27" s="9" t="n">
-        <v>1.5537</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="F29" s="6" t="n">
+        <v>4660541</v>
+      </c>
+      <c r="G29" s="7" t="n">
+        <v>2174.2</v>
+      </c>
+      <c r="H29" s="8" t="n">
+        <v>1013.2948</v>
+      </c>
+      <c r="I29" s="7" t="n">
+        <v>2174.2</v>
+      </c>
+      <c r="J29" s="8" t="n">
+        <v>1013.2948</v>
+      </c>
+      <c r="K29" s="7" t="n">
+        <v>2157.8</v>
+      </c>
+      <c r="L29" s="8" t="n">
+        <v>1005.6515</v>
+      </c>
+      <c r="M29" s="9" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="N29" s="10" t="n">
+        <v>0.01009</v>
+      </c>
+      <c r="O29" s="9" t="n">
+        <v>1.3281</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="n"/>
+      <c r="B30" s="11" t="n"/>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>Diversified Fmcg — subtotal</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="n"/>
+      <c r="E30" s="11" t="n"/>
+      <c r="F30" s="11" t="n"/>
+      <c r="G30" s="11" t="n"/>
+      <c r="H30" s="11" t="n"/>
+      <c r="I30" s="11" t="n"/>
+      <c r="J30" s="13" t="n">
+        <v>1013.295</v>
+      </c>
+      <c r="K30" s="11" t="n"/>
+      <c r="L30" s="11" t="n"/>
+      <c r="M30" s="11" t="n"/>
+      <c r="N30" s="11" t="n"/>
+      <c r="O30" s="14" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>INE030A01027</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>Hindustan Unilever Ltd.</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>Diversified Fmcg</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>INE205A01025</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Vedanta Ltd.</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Diversified Metals</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>structural</t>
         </is>
       </c>
-      <c r="F28" s="6" t="n">
-        <v>5347313</v>
-      </c>
-      <c r="G28" s="7" t="n">
-        <v>2174.2</v>
-      </c>
-      <c r="H28" s="8" t="n">
-        <v>1162.6128</v>
-      </c>
-      <c r="I28" s="7" t="n">
-        <v>2174.2</v>
-      </c>
-      <c r="J28" s="8" t="n">
-        <v>1162.6128</v>
-      </c>
-      <c r="K28" s="7" t="n">
-        <v>2157.8</v>
-      </c>
-      <c r="L28" s="8" t="n">
-        <v>1153.8432</v>
-      </c>
-      <c r="M28" s="9" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="N28" s="10" t="n">
-        <v>0.01158</v>
-      </c>
-      <c r="O28" s="9" t="n">
-        <v>1.5238</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="11" t="n"/>
-      <c r="B29" s="11" t="n"/>
-      <c r="C29" s="12" t="inlineStr">
-        <is>
-          <t>Diversified Fmcg — subtotal</t>
-        </is>
-      </c>
-      <c r="D29" s="11" t="n"/>
-      <c r="E29" s="11" t="n"/>
-      <c r="F29" s="11" t="n"/>
-      <c r="G29" s="11" t="n"/>
-      <c r="H29" s="11" t="n"/>
-      <c r="I29" s="11" t="n"/>
-      <c r="J29" s="13" t="n">
-        <v>2348.022</v>
-      </c>
-      <c r="K29" s="11" t="n"/>
-      <c r="L29" s="11" t="n"/>
-      <c r="M29" s="11" t="n"/>
-      <c r="N29" s="11" t="n"/>
-      <c r="O29" s="14" t="n">
-        <v>3.08</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>INE205A01025</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>Vedanta Ltd.</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>Diversified Metals</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>structural</t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="n">
-        <v>58355941</v>
-      </c>
-      <c r="G30" s="7" t="n">
+      <c r="F31" s="6" t="n">
+        <v>108797483</v>
+      </c>
+      <c r="G31" s="7" t="n">
         <v>273.45</v>
       </c>
-      <c r="H30" s="8" t="n">
-        <v>1595.7432</v>
-      </c>
-      <c r="I30" s="7" t="n">
+      <c r="H31" s="8" t="n">
+        <v>2975.0672</v>
+      </c>
+      <c r="I31" s="7" t="n">
         <v>273.45</v>
       </c>
-      <c r="J30" s="8" t="n">
-        <v>1595.7432</v>
-      </c>
-      <c r="K30" s="7" t="n">
+      <c r="J31" s="8" t="n">
+        <v>2975.0672</v>
+      </c>
+      <c r="K31" s="7" t="n">
         <v>282.55</v>
       </c>
-      <c r="L30" s="8" t="n">
-        <v>1648.8471</v>
-      </c>
-      <c r="M30" s="9" t="n">
+      <c r="L31" s="8" t="n">
+        <v>3074.0729</v>
+      </c>
+      <c r="M31" s="9" t="n">
         <v>-3.2207</v>
       </c>
-      <c r="N30" s="10" t="n">
-        <v>-0.06736</v>
-      </c>
-      <c r="O30" s="9" t="n">
-        <v>2.0915</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="11" t="n"/>
-      <c r="B31" s="11" t="n"/>
-      <c r="C31" s="12" t="inlineStr">
+      <c r="N31" s="10" t="n">
+        <v>-0.12558</v>
+      </c>
+      <c r="O31" s="9" t="n">
+        <v>3.8993</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="n"/>
+      <c r="B32" s="11" t="n"/>
+      <c r="C32" s="12" t="inlineStr">
         <is>
           <t>Diversified Metals — subtotal</t>
         </is>
       </c>
-      <c r="D31" s="11" t="n"/>
-      <c r="E31" s="11" t="n"/>
-      <c r="F31" s="11" t="n"/>
-      <c r="G31" s="11" t="n"/>
-      <c r="H31" s="11" t="n"/>
-      <c r="I31" s="11" t="n"/>
-      <c r="J31" s="13" t="n">
-        <v>1595.743</v>
-      </c>
-      <c r="K31" s="11" t="n"/>
-      <c r="L31" s="11" t="n"/>
-      <c r="M31" s="11" t="n"/>
-      <c r="N31" s="11" t="n"/>
-      <c r="O31" s="14" t="n">
-        <v>2.09</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>INE1CLE01013</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>Vedanta Iron And Steel Ltd.</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>Ferrous Metals</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>structural</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="n">
-        <v>369111583</v>
-      </c>
-      <c r="G32" s="7" t="n">
-        <v>30.88</v>
-      </c>
-      <c r="H32" s="8" t="n">
-        <v>1139.8166</v>
-      </c>
-      <c r="I32" s="7" t="n">
-        <v>30.88</v>
-      </c>
-      <c r="J32" s="8" t="n">
-        <v>1139.8166</v>
-      </c>
-      <c r="K32" s="7" t="n">
-        <v>29.41</v>
-      </c>
-      <c r="L32" s="8" t="n">
-        <v>1085.5572</v>
-      </c>
-      <c r="M32" s="9" t="n">
-        <v>4.9983</v>
-      </c>
-      <c r="N32" s="10" t="n">
-        <v>0.07467</v>
-      </c>
-      <c r="O32" s="9" t="n">
-        <v>1.4939</v>
+      <c r="D32" s="11" t="n"/>
+      <c r="E32" s="11" t="n"/>
+      <c r="F32" s="11" t="n"/>
+      <c r="G32" s="11" t="n"/>
+      <c r="H32" s="11" t="n"/>
+      <c r="I32" s="11" t="n"/>
+      <c r="J32" s="13" t="n">
+        <v>2975.067</v>
+      </c>
+      <c r="K32" s="11" t="n"/>
+      <c r="L32" s="11" t="n"/>
+      <c r="M32" s="11" t="n"/>
+      <c r="N32" s="11" t="n"/>
+      <c r="O32" s="14" t="n">
+        <v>3.9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>INE081A01020</t>
+          <t>INE117A01022</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Tata Steel Ltd.</t>
+          <t>ABB India Ltd.</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Ferrous Metals</t>
+          <t>Electrical Equipment</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>structural</t>
+          <t>cyclical</t>
         </is>
       </c>
       <c r="F33" s="6" t="n">
-        <v>59192424</v>
+        <v>1703512</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>188.71</v>
+        <v>6993</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>1117.0202</v>
+        <v>1191.2659</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>188.71</v>
+        <v>6993</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>1117.0202</v>
+        <v>1191.2659</v>
       </c>
       <c r="K33" s="7" t="n">
-        <v>190.16</v>
+        <v>6967.5</v>
       </c>
       <c r="L33" s="8" t="n">
-        <v>1125.6031</v>
+        <v>1186.922</v>
       </c>
       <c r="M33" s="9" t="n">
-        <v>-0.7625</v>
+        <v>0.366</v>
       </c>
       <c r="N33" s="10" t="n">
-        <v>-0.01116</v>
+        <v>0.00571</v>
       </c>
       <c r="O33" s="9" t="n">
-        <v>1.464</v>
+        <v>1.5614</v>
       </c>
     </row>
     <row r="34">
@@ -1928,7 +1868,7 @@
       <c r="B34" s="11" t="n"/>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>Ferrous Metals — subtotal</t>
+          <t>Electrical Equipment — subtotal</t>
         </is>
       </c>
       <c r="D34" s="11" t="n"/>
@@ -1938,33 +1878,33 @@
       <c r="H34" s="11" t="n"/>
       <c r="I34" s="11" t="n"/>
       <c r="J34" s="13" t="n">
-        <v>2256.837</v>
+        <v>1191.266</v>
       </c>
       <c r="K34" s="11" t="n"/>
       <c r="L34" s="11" t="n"/>
       <c r="M34" s="11" t="n"/>
       <c r="N34" s="11" t="n"/>
       <c r="O34" s="14" t="n">
-        <v>2.96</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>INE437A01024</t>
+          <t>INE081A01020</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Apollo Hospitals Enterprise Ltd.</t>
+          <t>Tata Steel Ltd.</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Healthcare Services</t>
+          <t>Ferrous Metals</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -1973,133 +1913,133 @@
         </is>
       </c>
       <c r="F35" s="6" t="n">
-        <v>1512326</v>
+        <v>90918280</v>
       </c>
       <c r="G35" s="7" t="n">
-        <v>8592</v>
+        <v>188.71</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>1299.3905</v>
+        <v>1715.7189</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>8592</v>
+        <v>188.71</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>1299.3905</v>
+        <v>1715.7189</v>
       </c>
       <c r="K35" s="7" t="n">
-        <v>8573.5</v>
+        <v>190.16</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>1296.5927</v>
+        <v>1728.902</v>
       </c>
       <c r="M35" s="9" t="n">
-        <v>0.2158</v>
+        <v>-0.7625</v>
       </c>
       <c r="N35" s="10" t="n">
-        <v>0.00368</v>
+        <v>-0.01715</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>1.7031</v>
+        <v>2.2487</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="11" t="n"/>
-      <c r="B36" s="11" t="n"/>
-      <c r="C36" s="12" t="inlineStr">
-        <is>
-          <t>Healthcare Services — subtotal</t>
-        </is>
-      </c>
-      <c r="D36" s="11" t="n"/>
-      <c r="E36" s="11" t="n"/>
-      <c r="F36" s="11" t="n"/>
-      <c r="G36" s="11" t="n"/>
-      <c r="H36" s="11" t="n"/>
-      <c r="I36" s="11" t="n"/>
-      <c r="J36" s="13" t="n">
-        <v>1299.39</v>
-      </c>
-      <c r="K36" s="11" t="n"/>
-      <c r="L36" s="11" t="n"/>
-      <c r="M36" s="11" t="n"/>
-      <c r="N36" s="11" t="n"/>
-      <c r="O36" s="14" t="n">
-        <v>1.7</v>
+      <c r="A36" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>INE1CLE01013</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Vedanta Iron And Steel Ltd.</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Ferrous Metals</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>375570046</v>
+      </c>
+      <c r="G36" s="7" t="n">
+        <v>30.88</v>
+      </c>
+      <c r="H36" s="8" t="n">
+        <v>1159.7603</v>
+      </c>
+      <c r="I36" s="7" t="n">
+        <v>30.88</v>
+      </c>
+      <c r="J36" s="8" t="n">
+        <v>1159.7603</v>
+      </c>
+      <c r="K36" s="7" t="n">
+        <v>29.41</v>
+      </c>
+      <c r="L36" s="8" t="n">
+        <v>1104.5515</v>
+      </c>
+      <c r="M36" s="9" t="n">
+        <v>4.9983</v>
+      </c>
+      <c r="N36" s="10" t="n">
+        <v>0.07598000000000001</v>
+      </c>
+      <c r="O36" s="9" t="n">
+        <v>1.5201</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>INE298A01020</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>Cummins India Ltd.</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>Industrial Products</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>structural</t>
-        </is>
-      </c>
-      <c r="F37" s="6" t="n">
-        <v>2303068</v>
-      </c>
-      <c r="G37" s="7" t="n">
-        <v>5642</v>
-      </c>
-      <c r="H37" s="8" t="n">
-        <v>1299.391</v>
-      </c>
-      <c r="I37" s="7" t="n">
-        <v>5642</v>
-      </c>
-      <c r="J37" s="8" t="n">
-        <v>1299.391</v>
-      </c>
-      <c r="K37" s="7" t="n">
-        <v>5555.5</v>
-      </c>
-      <c r="L37" s="8" t="n">
-        <v>1279.4694</v>
-      </c>
-      <c r="M37" s="9" t="n">
-        <v>1.557</v>
-      </c>
-      <c r="N37" s="10" t="n">
-        <v>0.02652</v>
-      </c>
-      <c r="O37" s="9" t="n">
-        <v>1.7031</v>
+      <c r="A37" s="11" t="n"/>
+      <c r="B37" s="11" t="n"/>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>Ferrous Metals — subtotal</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="n"/>
+      <c r="E37" s="11" t="n"/>
+      <c r="F37" s="11" t="n"/>
+      <c r="G37" s="11" t="n"/>
+      <c r="H37" s="11" t="n"/>
+      <c r="I37" s="11" t="n"/>
+      <c r="J37" s="13" t="n">
+        <v>2875.479</v>
+      </c>
+      <c r="K37" s="11" t="n"/>
+      <c r="L37" s="11" t="n"/>
+      <c r="M37" s="11" t="n"/>
+      <c r="N37" s="11" t="n"/>
+      <c r="O37" s="14" t="n">
+        <v>3.77</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>INE195A01028</t>
+          <t>INE129A01019</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Supreme Industries Ltd.</t>
+          <t>GAIL (India) Ltd.</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Industrial Products</t>
+          <t>Gas</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -2108,34 +2048,34 @@
         </is>
       </c>
       <c r="F38" s="6" t="n">
-        <v>2806709</v>
+        <v>72864529</v>
       </c>
       <c r="G38" s="7" t="n">
-        <v>3421.9</v>
+        <v>172.85</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>960.4278</v>
+        <v>1259.4634</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>3421.9</v>
+        <v>172.85</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>960.4278</v>
+        <v>1259.4634</v>
       </c>
       <c r="K38" s="7" t="n">
-        <v>3534.5768</v>
+        <v>174.93</v>
       </c>
       <c r="L38" s="8" t="n">
-        <v>992.0529</v>
+        <v>1274.6192</v>
       </c>
       <c r="M38" s="9" t="n">
-        <v>-3.1878</v>
+        <v>-1.189</v>
       </c>
       <c r="N38" s="10" t="n">
-        <v>-0.04013</v>
+        <v>-0.01963</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>1.2588</v>
+        <v>1.6507</v>
       </c>
     </row>
     <row r="39">
@@ -2143,7 +2083,7 @@
       <c r="B39" s="11" t="n"/>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Industrial Products — subtotal</t>
+          <t>Gas — subtotal</t>
         </is>
       </c>
       <c r="D39" s="11" t="n"/>
@@ -2153,143 +2093,113 @@
       <c r="H39" s="11" t="n"/>
       <c r="I39" s="11" t="n"/>
       <c r="J39" s="13" t="n">
-        <v>2259.819</v>
+        <v>1259.463</v>
       </c>
       <c r="K39" s="11" t="n"/>
       <c r="L39" s="11" t="n"/>
       <c r="M39" s="11" t="n"/>
       <c r="N39" s="11" t="n"/>
       <c r="O39" s="14" t="n">
-        <v>2.96</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>INE0J1Y01017</t>
+          <t>INE437A01024</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Life Insurance Corporation of India</t>
+          <t>Apollo Hospitals Enterprise Ltd.</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Healthcare Services</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>tactical</t>
+          <t>structural</t>
         </is>
       </c>
       <c r="F40" s="6" t="n">
-        <v>53309007</v>
+        <v>1669687</v>
       </c>
       <c r="G40" s="7" t="n">
-        <v>423.35</v>
+        <v>8592</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>2256.8368</v>
+        <v>1434.5951</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>423.35</v>
+        <v>8592</v>
       </c>
       <c r="J40" s="8" t="n">
-        <v>2256.8368</v>
+        <v>1434.5951</v>
       </c>
       <c r="K40" s="7" t="n">
-        <v>426.525</v>
+        <v>8573.5</v>
       </c>
       <c r="L40" s="8" t="n">
-        <v>2273.7624</v>
+        <v>1431.5061</v>
       </c>
       <c r="M40" s="9" t="n">
-        <v>-0.7444</v>
+        <v>0.2158</v>
       </c>
       <c r="N40" s="10" t="n">
-        <v>-0.02202</v>
+        <v>0.00406</v>
       </c>
       <c r="O40" s="9" t="n">
-        <v>2.958</v>
+        <v>1.8803</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>INE726G01019</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>ICICI Prudential Life Insurance Company Ltd.</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="inlineStr">
-        <is>
-          <t>structural</t>
-        </is>
-      </c>
-      <c r="F41" s="6" t="n">
-        <v>26461478</v>
-      </c>
-      <c r="G41" s="7" t="n">
-        <v>491.05</v>
-      </c>
-      <c r="H41" s="8" t="n">
-        <v>1299.3909</v>
-      </c>
-      <c r="I41" s="7" t="n">
-        <v>491.05</v>
-      </c>
-      <c r="J41" s="8" t="n">
-        <v>1299.3909</v>
-      </c>
-      <c r="K41" s="7" t="n">
-        <v>496.35</v>
-      </c>
-      <c r="L41" s="8" t="n">
-        <v>1313.4155</v>
-      </c>
-      <c r="M41" s="9" t="n">
-        <v>-1.0678</v>
-      </c>
-      <c r="N41" s="10" t="n">
-        <v>-0.01819</v>
-      </c>
-      <c r="O41" s="9" t="n">
-        <v>1.7031</v>
+      <c r="A41" s="11" t="n"/>
+      <c r="B41" s="11" t="n"/>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>Healthcare Services — subtotal</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="n"/>
+      <c r="E41" s="11" t="n"/>
+      <c r="F41" s="11" t="n"/>
+      <c r="G41" s="11" t="n"/>
+      <c r="H41" s="11" t="n"/>
+      <c r="I41" s="11" t="n"/>
+      <c r="J41" s="13" t="n">
+        <v>1434.595</v>
+      </c>
+      <c r="K41" s="11" t="n"/>
+      <c r="L41" s="11" t="n"/>
+      <c r="M41" s="11" t="n"/>
+      <c r="N41" s="11" t="n"/>
+      <c r="O41" s="14" t="n">
+        <v>1.88</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>INE765G01017</t>
+          <t>INE298A01020</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>ICICI Lombard General Insurance Company Ltd.</t>
+          <t>Cummins India Ltd.</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Industrial Products</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -2298,243 +2208,243 @@
         </is>
       </c>
       <c r="F42" s="6" t="n">
-        <v>6159132</v>
+        <v>2825258</v>
       </c>
       <c r="G42" s="7" t="n">
-        <v>1813.6</v>
+        <v>5642</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>1117.0202</v>
+        <v>1594.0106</v>
       </c>
       <c r="I42" s="7" t="n">
-        <v>1813.6</v>
+        <v>5642</v>
       </c>
       <c r="J42" s="8" t="n">
-        <v>1117.0202</v>
+        <v>1594.0106</v>
       </c>
       <c r="K42" s="7" t="n">
-        <v>1821.1</v>
+        <v>5555.5</v>
       </c>
       <c r="L42" s="8" t="n">
-        <v>1121.6395</v>
+        <v>1569.5721</v>
       </c>
       <c r="M42" s="9" t="n">
-        <v>-0.4118</v>
+        <v>1.557</v>
       </c>
       <c r="N42" s="10" t="n">
-        <v>-0.00603</v>
+        <v>0.03253</v>
       </c>
       <c r="O42" s="9" t="n">
-        <v>1.464</v>
+        <v>2.0892</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>INE123W01016</t>
+          <t>INE195A01028</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>SBI Life Insurance Company Ltd.</t>
+          <t>Supreme Industries Ltd.</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
+          <t>Industrial Products</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>2806709</v>
+      </c>
+      <c r="G43" s="7" t="n">
+        <v>3421.9</v>
+      </c>
+      <c r="H43" s="8" t="n">
+        <v>960.4278</v>
+      </c>
+      <c r="I43" s="7" t="n">
+        <v>3421.9</v>
+      </c>
+      <c r="J43" s="8" t="n">
+        <v>960.4278</v>
+      </c>
+      <c r="K43" s="7" t="n">
+        <v>3534.5768</v>
+      </c>
+      <c r="L43" s="8" t="n">
+        <v>992.0529</v>
+      </c>
+      <c r="M43" s="9" t="n">
+        <v>-3.1878</v>
+      </c>
+      <c r="N43" s="10" t="n">
+        <v>-0.04013</v>
+      </c>
+      <c r="O43" s="9" t="n">
+        <v>1.2588</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="n"/>
+      <c r="B44" s="11" t="n"/>
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t>Industrial Products — subtotal</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="n"/>
+      <c r="E44" s="11" t="n"/>
+      <c r="F44" s="11" t="n"/>
+      <c r="G44" s="11" t="n"/>
+      <c r="H44" s="11" t="n"/>
+      <c r="I44" s="11" t="n"/>
+      <c r="J44" s="13" t="n">
+        <v>2554.438</v>
+      </c>
+      <c r="K44" s="11" t="n"/>
+      <c r="L44" s="11" t="n"/>
+      <c r="M44" s="11" t="n"/>
+      <c r="N44" s="11" t="n"/>
+      <c r="O44" s="14" t="n">
+        <v>3.35</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>INE0J1Y01017</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Life Insurance Corporation of India</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>structural</t>
-        </is>
-      </c>
-      <c r="F43" s="6" t="n">
-        <v>6140338</v>
-      </c>
-      <c r="G43" s="7" t="n">
-        <v>1744.9</v>
-      </c>
-      <c r="H43" s="8" t="n">
-        <v>1071.4276</v>
-      </c>
-      <c r="I43" s="7" t="n">
-        <v>1744.9</v>
-      </c>
-      <c r="J43" s="8" t="n">
-        <v>1071.4276</v>
-      </c>
-      <c r="K43" s="7" t="n">
-        <v>1767.7</v>
-      </c>
-      <c r="L43" s="8" t="n">
-        <v>1085.4275</v>
-      </c>
-      <c r="M43" s="9" t="n">
-        <v>-1.2898</v>
-      </c>
-      <c r="N43" s="10" t="n">
-        <v>-0.01811</v>
-      </c>
-      <c r="O43" s="9" t="n">
-        <v>1.4043</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>INE795G01014</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>HDFC Life Insurance Company Ltd.</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>structural</t>
-        </is>
-      </c>
-      <c r="F44" s="6" t="n">
-        <v>17132780</v>
-      </c>
-      <c r="G44" s="7" t="n">
-        <v>585.45</v>
-      </c>
-      <c r="H44" s="8" t="n">
-        <v>1003.0386</v>
-      </c>
-      <c r="I44" s="7" t="n">
-        <v>585.45</v>
-      </c>
-      <c r="J44" s="8" t="n">
-        <v>1003.0386</v>
-      </c>
-      <c r="K44" s="7" t="n">
-        <v>591.75</v>
-      </c>
-      <c r="L44" s="8" t="n">
-        <v>1013.8323</v>
-      </c>
-      <c r="M44" s="9" t="n">
-        <v>-1.0646</v>
-      </c>
-      <c r="N44" s="10" t="n">
-        <v>-0.014</v>
-      </c>
-      <c r="O44" s="9" t="n">
-        <v>1.3147</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="11" t="n"/>
-      <c r="B45" s="11" t="n"/>
-      <c r="C45" s="12" t="inlineStr">
-        <is>
-          <t>Insurance — subtotal</t>
-        </is>
-      </c>
-      <c r="D45" s="11" t="n"/>
-      <c r="E45" s="11" t="n"/>
-      <c r="F45" s="11" t="n"/>
-      <c r="G45" s="11" t="n"/>
-      <c r="H45" s="11" t="n"/>
-      <c r="I45" s="11" t="n"/>
-      <c r="J45" s="13" t="n">
-        <v>6747.714</v>
-      </c>
-      <c r="K45" s="11" t="n"/>
-      <c r="L45" s="11" t="n"/>
-      <c r="M45" s="11" t="n"/>
-      <c r="N45" s="11" t="n"/>
-      <c r="O45" s="14" t="n">
-        <v>8.84</v>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>tactical</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>41698433</v>
+      </c>
+      <c r="G45" s="7" t="n">
+        <v>423.35</v>
+      </c>
+      <c r="H45" s="8" t="n">
+        <v>1765.3032</v>
+      </c>
+      <c r="I45" s="7" t="n">
+        <v>423.35</v>
+      </c>
+      <c r="J45" s="8" t="n">
+        <v>1765.3032</v>
+      </c>
+      <c r="K45" s="7" t="n">
+        <v>426.525</v>
+      </c>
+      <c r="L45" s="8" t="n">
+        <v>1778.5424</v>
+      </c>
+      <c r="M45" s="9" t="n">
+        <v>-0.7444</v>
+      </c>
+      <c r="N45" s="10" t="n">
+        <v>-0.01722</v>
+      </c>
+      <c r="O45" s="9" t="n">
+        <v>2.3137</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>INE669C01036</t>
+          <t>INE765G01017</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Tech Mahindra Ltd.</t>
+          <t>ICICI Lombard General Insurance Company Ltd.</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>It - Software</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>tactical</t>
+          <t>structural</t>
         </is>
       </c>
       <c r="F46" s="6" t="n">
-        <v>12214303</v>
+        <v>6043108</v>
       </c>
       <c r="G46" s="7" t="n">
-        <v>1437.1</v>
+        <v>1813.6</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>1755.3175</v>
+        <v>1095.9781</v>
       </c>
       <c r="I46" s="7" t="n">
-        <v>1437.1</v>
+        <v>1813.6</v>
       </c>
       <c r="J46" s="8" t="n">
-        <v>1755.3175</v>
+        <v>1095.9781</v>
       </c>
       <c r="K46" s="7" t="n">
-        <v>1461.6</v>
+        <v>1821.1</v>
       </c>
       <c r="L46" s="8" t="n">
-        <v>1785.2425</v>
+        <v>1100.5104</v>
       </c>
       <c r="M46" s="9" t="n">
-        <v>-1.6762</v>
+        <v>-0.4118</v>
       </c>
       <c r="N46" s="10" t="n">
-        <v>-0.03856</v>
+        <v>-0.00592</v>
       </c>
       <c r="O46" s="9" t="n">
-        <v>2.3006</v>
+        <v>1.4365</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>INE075A01022</t>
+          <t>INE123W01016</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Wipro Ltd.</t>
+          <t>SBI Life Insurance Company Ltd.</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>It - Software</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -2543,188 +2453,188 @@
         </is>
       </c>
       <c r="F47" s="6" t="n">
-        <v>79461498</v>
+        <v>6258879</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>175</v>
+        <v>1744.9</v>
       </c>
       <c r="H47" s="8" t="n">
-        <v>1390.5762</v>
+        <v>1092.1118</v>
       </c>
       <c r="I47" s="7" t="n">
-        <v>175</v>
+        <v>1744.9</v>
       </c>
       <c r="J47" s="8" t="n">
-        <v>1390.5762</v>
+        <v>1092.1118</v>
       </c>
       <c r="K47" s="7" t="n">
-        <v>174.48</v>
+        <v>1767.7</v>
       </c>
       <c r="L47" s="8" t="n">
-        <v>1386.4442</v>
+        <v>1106.382</v>
       </c>
       <c r="M47" s="9" t="n">
-        <v>0.298</v>
+        <v>-1.2898</v>
       </c>
       <c r="N47" s="10" t="n">
-        <v>0.00543</v>
+        <v>-0.01846</v>
       </c>
       <c r="O47" s="9" t="n">
-        <v>1.8226</v>
+        <v>1.4314</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>INE009A01021</t>
+          <t>INE726G01019</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Infosys Ltd.</t>
+          <t>ICICI Prudential Life Insurance Company Ltd.</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v>21605441</v>
+      </c>
+      <c r="G48" s="7" t="n">
+        <v>491.05</v>
+      </c>
+      <c r="H48" s="8" t="n">
+        <v>1060.9352</v>
+      </c>
+      <c r="I48" s="7" t="n">
+        <v>491.05</v>
+      </c>
+      <c r="J48" s="8" t="n">
+        <v>1060.9352</v>
+      </c>
+      <c r="K48" s="7" t="n">
+        <v>496.35</v>
+      </c>
+      <c r="L48" s="8" t="n">
+        <v>1072.3861</v>
+      </c>
+      <c r="M48" s="9" t="n">
+        <v>-1.0678</v>
+      </c>
+      <c r="N48" s="10" t="n">
+        <v>-0.01485</v>
+      </c>
+      <c r="O48" s="9" t="n">
+        <v>1.3905</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="11" t="n"/>
+      <c r="B49" s="11" t="n"/>
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>Insurance — subtotal</t>
+        </is>
+      </c>
+      <c r="D49" s="11" t="n"/>
+      <c r="E49" s="11" t="n"/>
+      <c r="F49" s="11" t="n"/>
+      <c r="G49" s="11" t="n"/>
+      <c r="H49" s="11" t="n"/>
+      <c r="I49" s="11" t="n"/>
+      <c r="J49" s="13" t="n">
+        <v>5014.328</v>
+      </c>
+      <c r="K49" s="11" t="n"/>
+      <c r="L49" s="11" t="n"/>
+      <c r="M49" s="11" t="n"/>
+      <c r="N49" s="11" t="n"/>
+      <c r="O49" s="14" t="n">
+        <v>6.57</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>INE669C01036</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Tech Mahindra Ltd.</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
           <t>It - Software</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>structural</t>
-        </is>
-      </c>
-      <c r="F48" s="6" t="n">
-        <v>12698686</v>
-      </c>
-      <c r="G48" s="7" t="n">
-        <v>1041.2</v>
-      </c>
-      <c r="H48" s="8" t="n">
-        <v>1322.1872</v>
-      </c>
-      <c r="I48" s="7" t="n">
-        <v>1041.2</v>
-      </c>
-      <c r="J48" s="8" t="n">
-        <v>1322.1872</v>
-      </c>
-      <c r="K48" s="7" t="n">
-        <v>1056.6</v>
-      </c>
-      <c r="L48" s="8" t="n">
-        <v>1341.7432</v>
-      </c>
-      <c r="M48" s="9" t="n">
-        <v>-1.4575</v>
-      </c>
-      <c r="N48" s="10" t="n">
-        <v>-0.02526</v>
-      </c>
-      <c r="O48" s="9" t="n">
-        <v>1.7329</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>INE093A01041</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>Hexaware Technologies Ltd.</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>It - Software</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="E50" s="5" t="inlineStr">
         <is>
           <t>tactical</t>
         </is>
       </c>
-      <c r="F49" s="6" t="n">
-        <v>7736699</v>
-      </c>
-      <c r="G49" s="7" t="n">
-        <v>494.85</v>
-      </c>
-      <c r="H49" s="8" t="n">
-        <v>382.8506</v>
-      </c>
-      <c r="I49" s="7" t="n">
-        <v>494.85</v>
-      </c>
-      <c r="J49" s="8" t="n">
-        <v>382.8506</v>
-      </c>
-      <c r="K49" s="7" t="n">
-        <v>494.45</v>
-      </c>
-      <c r="L49" s="8" t="n">
-        <v>382.5411</v>
-      </c>
-      <c r="M49" s="9" t="n">
-        <v>0.0809</v>
-      </c>
-      <c r="N49" s="10" t="n">
-        <v>0.00041</v>
-      </c>
-      <c r="O49" s="9" t="n">
-        <v>0.5018</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="11" t="n"/>
-      <c r="B50" s="11" t="n"/>
-      <c r="C50" s="12" t="inlineStr">
-        <is>
-          <t>It - Software — subtotal</t>
-        </is>
-      </c>
-      <c r="D50" s="11" t="n"/>
-      <c r="E50" s="11" t="n"/>
-      <c r="F50" s="11" t="n"/>
-      <c r="G50" s="11" t="n"/>
-      <c r="H50" s="11" t="n"/>
-      <c r="I50" s="11" t="n"/>
-      <c r="J50" s="13" t="n">
-        <v>4850.931</v>
-      </c>
-      <c r="K50" s="11" t="n"/>
-      <c r="L50" s="11" t="n"/>
-      <c r="M50" s="11" t="n"/>
-      <c r="N50" s="11" t="n"/>
-      <c r="O50" s="14" t="n">
-        <v>6.36</v>
+      <c r="F50" s="6" t="n">
+        <v>9758320</v>
+      </c>
+      <c r="G50" s="7" t="n">
+        <v>1437.1</v>
+      </c>
+      <c r="H50" s="8" t="n">
+        <v>1402.3682</v>
+      </c>
+      <c r="I50" s="7" t="n">
+        <v>1437.1</v>
+      </c>
+      <c r="J50" s="8" t="n">
+        <v>1402.3682</v>
+      </c>
+      <c r="K50" s="7" t="n">
+        <v>1461.6</v>
+      </c>
+      <c r="L50" s="8" t="n">
+        <v>1426.2761</v>
+      </c>
+      <c r="M50" s="9" t="n">
+        <v>-1.6762</v>
+      </c>
+      <c r="N50" s="10" t="n">
+        <v>-0.03081</v>
+      </c>
+      <c r="O50" s="9" t="n">
+        <v>1.838</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>INE053A01029</t>
+          <t>INE075A01022</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>The Indian Hotels Company Ltd.</t>
+          <t>Wipro Ltd.</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Leisure Services</t>
+          <t>It - Software</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -2733,89 +2643,89 @@
         </is>
       </c>
       <c r="F51" s="6" t="n">
-        <v>13285866</v>
+        <v>68266394</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>720.65</v>
+        <v>175</v>
       </c>
       <c r="H51" s="8" t="n">
-        <v>957.4459000000001</v>
+        <v>1194.6619</v>
       </c>
       <c r="I51" s="7" t="n">
-        <v>720.65</v>
+        <v>175</v>
       </c>
       <c r="J51" s="8" t="n">
-        <v>957.4459000000001</v>
+        <v>1194.6619</v>
       </c>
       <c r="K51" s="7" t="n">
-        <v>725.5</v>
+        <v>174.48</v>
       </c>
       <c r="L51" s="8" t="n">
-        <v>963.8896</v>
+        <v>1191.112</v>
       </c>
       <c r="M51" s="9" t="n">
-        <v>-0.6685</v>
+        <v>0.298</v>
       </c>
       <c r="N51" s="10" t="n">
-        <v>-0.00839</v>
+        <v>0.00467</v>
       </c>
       <c r="O51" s="9" t="n">
-        <v>1.2549</v>
+        <v>1.5658</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>INE379A01028</t>
+          <t>INE093A01041</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>ITC Hotels Ltd</t>
+          <t>Hexaware Technologies Ltd.</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Leisure Services</t>
+          <t>It - Software</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>structural</t>
+          <t>tactical</t>
         </is>
       </c>
       <c r="F52" s="6" t="n">
-        <v>53404950</v>
+        <v>7736699</v>
       </c>
       <c r="G52" s="7" t="n">
-        <v>173.68</v>
+        <v>494.85</v>
       </c>
       <c r="H52" s="8" t="n">
-        <v>927.5372</v>
+        <v>382.8506</v>
       </c>
       <c r="I52" s="7" t="n">
-        <v>173.68</v>
+        <v>494.85</v>
       </c>
       <c r="J52" s="8" t="n">
-        <v>927.5372</v>
+        <v>382.8506</v>
       </c>
       <c r="K52" s="7" t="n">
-        <v>178.56</v>
+        <v>494.45</v>
       </c>
       <c r="L52" s="8" t="n">
-        <v>953.5988</v>
+        <v>382.5411</v>
       </c>
       <c r="M52" s="9" t="n">
-        <v>-2.733</v>
+        <v>0.0809</v>
       </c>
       <c r="N52" s="10" t="n">
-        <v>-0.03323</v>
+        <v>0.00041</v>
       </c>
       <c r="O52" s="9" t="n">
-        <v>1.2157</v>
+        <v>0.5018</v>
       </c>
     </row>
     <row r="53">
@@ -2823,7 +2733,7 @@
       <c r="B53" s="11" t="n"/>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Leisure Services — subtotal</t>
+          <t>It - Software — subtotal</t>
         </is>
       </c>
       <c r="D53" s="11" t="n"/>
@@ -2833,19 +2743,19 @@
       <c r="H53" s="11" t="n"/>
       <c r="I53" s="11" t="n"/>
       <c r="J53" s="13" t="n">
-        <v>1884.983</v>
+        <v>2979.881</v>
       </c>
       <c r="K53" s="11" t="n"/>
       <c r="L53" s="11" t="n"/>
       <c r="M53" s="11" t="n"/>
       <c r="N53" s="11" t="n"/>
       <c r="O53" s="14" t="n">
-        <v>2.47</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
@@ -2868,34 +2778,34 @@
         </is>
       </c>
       <c r="F54" s="6" t="n">
-        <v>25739952</v>
+        <v>26190332</v>
       </c>
       <c r="G54" s="7" t="n">
         <v>442.82</v>
       </c>
       <c r="H54" s="8" t="n">
-        <v>1139.8166</v>
+        <v>1159.7603</v>
       </c>
       <c r="I54" s="7" t="n">
         <v>442.82</v>
       </c>
       <c r="J54" s="8" t="n">
-        <v>1139.8166</v>
+        <v>1159.7603</v>
       </c>
       <c r="K54" s="7" t="n">
         <v>463.13</v>
       </c>
       <c r="L54" s="8" t="n">
-        <v>1192.0944</v>
+        <v>1212.9528</v>
       </c>
       <c r="M54" s="9" t="n">
         <v>-4.3854</v>
       </c>
       <c r="N54" s="10" t="n">
-        <v>-0.06551</v>
+        <v>-0.06666</v>
       </c>
       <c r="O54" s="9" t="n">
-        <v>1.4939</v>
+        <v>1.5201</v>
       </c>
     </row>
     <row r="55">
@@ -2913,19 +2823,19 @@
       <c r="H55" s="11" t="n"/>
       <c r="I55" s="11" t="n"/>
       <c r="J55" s="13" t="n">
-        <v>1139.817</v>
+        <v>1159.76</v>
       </c>
       <c r="K55" s="11" t="n"/>
       <c r="L55" s="11" t="n"/>
       <c r="M55" s="11" t="n"/>
       <c r="N55" s="11" t="n"/>
       <c r="O55" s="14" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
@@ -2948,39 +2858,39 @@
         </is>
       </c>
       <c r="F56" s="6" t="n">
-        <v>95840432</v>
+        <v>104040646</v>
       </c>
       <c r="G56" s="7" t="n">
         <v>233.1</v>
       </c>
       <c r="H56" s="8" t="n">
-        <v>2234.0405</v>
+        <v>2425.1875</v>
       </c>
       <c r="I56" s="7" t="n">
         <v>233.1</v>
       </c>
       <c r="J56" s="8" t="n">
-        <v>2234.0405</v>
+        <v>2425.1875</v>
       </c>
       <c r="K56" s="7" t="n">
         <v>240</v>
       </c>
       <c r="L56" s="8" t="n">
-        <v>2300.1704</v>
+        <v>2496.9755</v>
       </c>
       <c r="M56" s="9" t="n">
         <v>-2.875</v>
       </c>
       <c r="N56" s="10" t="n">
-        <v>-0.08418</v>
+        <v>-0.09138</v>
       </c>
       <c r="O56" s="9" t="n">
-        <v>2.9281</v>
+        <v>3.1786</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
@@ -3003,34 +2913,34 @@
         </is>
       </c>
       <c r="F57" s="6" t="n">
-        <v>41468253</v>
+        <v>46612357</v>
       </c>
       <c r="G57" s="7" t="n">
         <v>406.8</v>
       </c>
       <c r="H57" s="8" t="n">
-        <v>1686.9285</v>
+        <v>1896.1907</v>
       </c>
       <c r="I57" s="7" t="n">
         <v>406.8</v>
       </c>
       <c r="J57" s="8" t="n">
-        <v>1686.9285</v>
+        <v>1896.1907</v>
       </c>
       <c r="K57" s="7" t="n">
         <v>418.05</v>
       </c>
       <c r="L57" s="8" t="n">
-        <v>1733.5803</v>
+        <v>1948.6296</v>
       </c>
       <c r="M57" s="9" t="n">
         <v>-2.6911</v>
       </c>
       <c r="N57" s="10" t="n">
-        <v>-0.0595</v>
+        <v>-0.06688</v>
       </c>
       <c r="O57" s="9" t="n">
-        <v>2.211</v>
+        <v>2.4853</v>
       </c>
     </row>
     <row r="58">
@@ -3048,218 +2958,218 @@
       <c r="H58" s="11" t="n"/>
       <c r="I58" s="11" t="n"/>
       <c r="J58" s="13" t="n">
-        <v>3920.969</v>
+        <v>4321.378</v>
       </c>
       <c r="K58" s="11" t="n"/>
       <c r="L58" s="11" t="n"/>
       <c r="M58" s="11" t="n"/>
       <c r="N58" s="11" t="n"/>
       <c r="O58" s="14" t="n">
-        <v>5.14</v>
+        <v>5.66</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
+          <t>INE242A01010</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>Indian Oil Corporation Ltd.</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>Petroleum Products</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>cyclical</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v>83572206</v>
+      </c>
+      <c r="G59" s="7" t="n">
+        <v>143.89</v>
+      </c>
+      <c r="H59" s="8" t="n">
+        <v>1202.5205</v>
+      </c>
+      <c r="I59" s="7" t="n">
+        <v>143.89</v>
+      </c>
+      <c r="J59" s="8" t="n">
+        <v>1202.5205</v>
+      </c>
+      <c r="K59" s="7" t="n">
+        <v>146.3</v>
+      </c>
+      <c r="L59" s="8" t="n">
+        <v>1222.6614</v>
+      </c>
+      <c r="M59" s="9" t="n">
+        <v>-1.6473</v>
+      </c>
+      <c r="N59" s="10" t="n">
+        <v>-0.02596</v>
+      </c>
+      <c r="O59" s="9" t="n">
+        <v>1.5761</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
           <t>INE002A01018</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
+      <c r="C60" s="5" t="inlineStr">
         <is>
           <t>Reliance Industries Ltd.</t>
         </is>
       </c>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="D60" s="5" t="inlineStr">
         <is>
           <t>Petroleum Products</t>
         </is>
       </c>
-      <c r="E59" s="5" t="inlineStr">
+      <c r="E60" s="5" t="inlineStr">
         <is>
           <t>structural</t>
         </is>
       </c>
-      <c r="F59" s="6" t="n">
-        <v>8474473</v>
-      </c>
-      <c r="G59" s="7" t="n">
+      <c r="F60" s="6" t="n">
+        <v>8097736</v>
+      </c>
+      <c r="G60" s="7" t="n">
         <v>1318.1</v>
       </c>
-      <c r="H59" s="8" t="n">
-        <v>1117.0203</v>
-      </c>
-      <c r="I59" s="7" t="n">
+      <c r="H60" s="8" t="n">
+        <v>1067.3626</v>
+      </c>
+      <c r="I60" s="7" t="n">
         <v>1318.1</v>
       </c>
-      <c r="J59" s="8" t="n">
-        <v>1117.0203</v>
-      </c>
-      <c r="K59" s="7" t="n">
+      <c r="J60" s="8" t="n">
+        <v>1067.3626</v>
+      </c>
+      <c r="K60" s="7" t="n">
         <v>1313.6</v>
       </c>
-      <c r="L59" s="8" t="n">
-        <v>1113.2068</v>
-      </c>
-      <c r="M59" s="9" t="n">
+      <c r="L60" s="8" t="n">
+        <v>1063.7186</v>
+      </c>
+      <c r="M60" s="9" t="n">
         <v>0.3426</v>
       </c>
-      <c r="N59" s="10" t="n">
-        <v>0.00502</v>
-      </c>
-      <c r="O59" s="9" t="n">
-        <v>1.464</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="11" t="n"/>
-      <c r="B60" s="11" t="n"/>
-      <c r="C60" s="12" t="inlineStr">
-        <is>
-          <t>Petroleum Products — subtotal</t>
-        </is>
-      </c>
-      <c r="D60" s="11" t="n"/>
-      <c r="E60" s="11" t="n"/>
-      <c r="F60" s="11" t="n"/>
-      <c r="G60" s="11" t="n"/>
-      <c r="H60" s="11" t="n"/>
-      <c r="I60" s="11" t="n"/>
-      <c r="J60" s="13" t="n">
-        <v>1117.02</v>
-      </c>
-      <c r="K60" s="11" t="n"/>
-      <c r="L60" s="11" t="n"/>
-      <c r="M60" s="11" t="n"/>
-      <c r="N60" s="11" t="n"/>
-      <c r="O60" s="14" t="n">
-        <v>1.46</v>
+      <c r="N60" s="10" t="n">
+        <v>0.00479</v>
+      </c>
+      <c r="O60" s="9" t="n">
+        <v>1.399</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>INE010B01027</t>
+          <t>INE029A01011</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Zydus Lifesciences Ltd.</t>
+          <t>Bharat Petroleum Corporation Ltd.</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Pharmaceuticals &amp; Biotechnology</t>
+          <t>Petroleum Products</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>tactical</t>
+          <t>cyclical</t>
         </is>
       </c>
       <c r="F61" s="6" t="n">
-        <v>18834812</v>
+        <v>33286169</v>
       </c>
       <c r="G61" s="7" t="n">
-        <v>1101.4</v>
+        <v>309.75</v>
       </c>
       <c r="H61" s="8" t="n">
-        <v>2074.4662</v>
+        <v>1031.0391</v>
       </c>
       <c r="I61" s="7" t="n">
-        <v>1101.4</v>
+        <v>309.75</v>
       </c>
       <c r="J61" s="8" t="n">
-        <v>2074.4662</v>
+        <v>1031.0391</v>
       </c>
       <c r="K61" s="7" t="n">
-        <v>1099.3</v>
+        <v>315.7</v>
       </c>
       <c r="L61" s="8" t="n">
-        <v>2070.5109</v>
+        <v>1050.8444</v>
       </c>
       <c r="M61" s="9" t="n">
-        <v>0.191</v>
+        <v>-1.8847</v>
       </c>
       <c r="N61" s="10" t="n">
-        <v>0.00519</v>
+        <v>-0.02547</v>
       </c>
       <c r="O61" s="9" t="n">
-        <v>2.7189</v>
+        <v>1.3513</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="n">
-        <v>41</v>
-      </c>
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>INE326A01037</t>
-        </is>
-      </c>
-      <c r="C62" s="5" t="inlineStr">
-        <is>
-          <t>Lupin Ltd.</t>
-        </is>
-      </c>
-      <c r="D62" s="5" t="inlineStr">
-        <is>
-          <t>Pharmaceuticals &amp; Biotechnology</t>
-        </is>
-      </c>
-      <c r="E62" s="5" t="inlineStr">
-        <is>
-          <t>structural</t>
-        </is>
-      </c>
-      <c r="F62" s="6" t="n">
-        <v>6128308</v>
-      </c>
-      <c r="G62" s="7" t="n">
-        <v>2343.5</v>
-      </c>
-      <c r="H62" s="8" t="n">
-        <v>1436.169</v>
-      </c>
-      <c r="I62" s="7" t="n">
-        <v>2343.5</v>
-      </c>
-      <c r="J62" s="8" t="n">
-        <v>1436.169</v>
-      </c>
-      <c r="K62" s="7" t="n">
-        <v>2367.6</v>
-      </c>
-      <c r="L62" s="8" t="n">
-        <v>1450.9382</v>
-      </c>
-      <c r="M62" s="9" t="n">
-        <v>-1.0179</v>
-      </c>
-      <c r="N62" s="10" t="n">
-        <v>-0.01916</v>
-      </c>
-      <c r="O62" s="9" t="n">
-        <v>1.8823</v>
+      <c r="A62" s="11" t="n"/>
+      <c r="B62" s="11" t="n"/>
+      <c r="C62" s="12" t="inlineStr">
+        <is>
+          <t>Petroleum Products — subtotal</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="n"/>
+      <c r="E62" s="11" t="n"/>
+      <c r="F62" s="11" t="n"/>
+      <c r="G62" s="11" t="n"/>
+      <c r="H62" s="11" t="n"/>
+      <c r="I62" s="11" t="n"/>
+      <c r="J62" s="13" t="n">
+        <v>3300.922</v>
+      </c>
+      <c r="K62" s="11" t="n"/>
+      <c r="L62" s="11" t="n"/>
+      <c r="M62" s="11" t="n"/>
+      <c r="N62" s="11" t="n"/>
+      <c r="O62" s="14" t="n">
+        <v>4.33</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>INE059A01026</t>
+          <t>INE010B01027</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Cipla Ltd.</t>
+          <t>Zydus Lifesciences Ltd.</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
@@ -3269,192 +3179,222 @@
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>structural</t>
+          <t>tactical</t>
         </is>
       </c>
       <c r="F63" s="6" t="n">
-        <v>8231437</v>
+        <v>16928814</v>
       </c>
       <c r="G63" s="7" t="n">
-        <v>1440.1</v>
+        <v>1101.4</v>
       </c>
       <c r="H63" s="8" t="n">
-        <v>1185.4092</v>
+        <v>1864.5396</v>
       </c>
       <c r="I63" s="7" t="n">
-        <v>1440.1</v>
+        <v>1101.4</v>
       </c>
       <c r="J63" s="8" t="n">
-        <v>1185.4092</v>
+        <v>1864.5396</v>
       </c>
       <c r="K63" s="7" t="n">
-        <v>1437.9</v>
+        <v>1099.3</v>
       </c>
       <c r="L63" s="8" t="n">
-        <v>1183.5983</v>
+        <v>1860.9845</v>
       </c>
       <c r="M63" s="9" t="n">
-        <v>0.153</v>
+        <v>0.191</v>
       </c>
       <c r="N63" s="10" t="n">
-        <v>0.00238</v>
+        <v>0.00467</v>
       </c>
       <c r="O63" s="9" t="n">
-        <v>1.5537</v>
+        <v>2.4438</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
+          <t>INE326A01037</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>Lupin Ltd.</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>Pharmaceuticals &amp; Biotechnology</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="n">
+        <v>6490613</v>
+      </c>
+      <c r="G64" s="7" t="n">
+        <v>2343.5</v>
+      </c>
+      <c r="H64" s="8" t="n">
+        <v>1521.0752</v>
+      </c>
+      <c r="I64" s="7" t="n">
+        <v>2343.5</v>
+      </c>
+      <c r="J64" s="8" t="n">
+        <v>1521.0752</v>
+      </c>
+      <c r="K64" s="7" t="n">
+        <v>2367.6</v>
+      </c>
+      <c r="L64" s="8" t="n">
+        <v>1536.7175</v>
+      </c>
+      <c r="M64" s="9" t="n">
+        <v>-1.0179</v>
+      </c>
+      <c r="N64" s="10" t="n">
+        <v>-0.02029</v>
+      </c>
+      <c r="O64" s="9" t="n">
+        <v>1.9936</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
           <t>INE044A01036</t>
         </is>
       </c>
-      <c r="C64" s="5" t="inlineStr">
+      <c r="C65" s="5" t="inlineStr">
         <is>
           <t>Sun Pharmaceutical Industries Ltd.</t>
         </is>
       </c>
-      <c r="D64" s="5" t="inlineStr">
+      <c r="D65" s="5" t="inlineStr">
         <is>
           <t>Pharmaceuticals &amp; Biotechnology</t>
         </is>
       </c>
-      <c r="E64" s="5" t="inlineStr">
+      <c r="E65" s="5" t="inlineStr">
         <is>
           <t>structural</t>
         </is>
       </c>
-      <c r="F64" s="6" t="n">
-        <v>6118835</v>
-      </c>
-      <c r="G64" s="7" t="n">
+      <c r="F65" s="6" t="n">
+        <v>6593469</v>
+      </c>
+      <c r="G65" s="7" t="n">
         <v>1862.8</v>
       </c>
-      <c r="H64" s="8" t="n">
-        <v>1139.8166</v>
-      </c>
-      <c r="I64" s="7" t="n">
+      <c r="H65" s="8" t="n">
+        <v>1228.2314</v>
+      </c>
+      <c r="I65" s="7" t="n">
         <v>1862.8</v>
       </c>
-      <c r="J64" s="8" t="n">
-        <v>1139.8166</v>
-      </c>
-      <c r="K64" s="7" t="n">
+      <c r="J65" s="8" t="n">
+        <v>1228.2314</v>
+      </c>
+      <c r="K65" s="7" t="n">
         <v>1874.4</v>
       </c>
-      <c r="L64" s="8" t="n">
-        <v>1146.9144</v>
-      </c>
-      <c r="M64" s="9" t="n">
+      <c r="L65" s="8" t="n">
+        <v>1235.8798</v>
+      </c>
+      <c r="M65" s="9" t="n">
         <v>-0.6189</v>
       </c>
-      <c r="N64" s="10" t="n">
-        <v>-0.00925</v>
-      </c>
-      <c r="O64" s="9" t="n">
-        <v>1.4939</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="11" t="n"/>
-      <c r="B65" s="11" t="n"/>
-      <c r="C65" s="12" t="inlineStr">
-        <is>
-          <t>Pharmaceuticals &amp; Biotechnology — subtotal</t>
-        </is>
-      </c>
-      <c r="D65" s="11" t="n"/>
-      <c r="E65" s="11" t="n"/>
-      <c r="F65" s="11" t="n"/>
-      <c r="G65" s="11" t="n"/>
-      <c r="H65" s="11" t="n"/>
-      <c r="I65" s="11" t="n"/>
-      <c r="J65" s="13" t="n">
-        <v>5835.861</v>
-      </c>
-      <c r="K65" s="11" t="n"/>
-      <c r="L65" s="11" t="n"/>
-      <c r="M65" s="11" t="n"/>
-      <c r="N65" s="11" t="n"/>
-      <c r="O65" s="14" t="n">
-        <v>7.65</v>
+      <c r="N65" s="10" t="n">
+        <v>-0.00996</v>
+      </c>
+      <c r="O65" s="9" t="n">
+        <v>1.6098</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>INE733E01010</t>
+          <t>INE089A01031</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>NTPC Ltd.</t>
+          <t>Dr. Reddy's Laboratories Ltd.</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Pharmaceuticals &amp; Biotechnology</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>structural</t>
+          <t>cyclical</t>
         </is>
       </c>
       <c r="F66" s="6" t="n">
-        <v>42089520</v>
+        <v>9001957</v>
       </c>
       <c r="G66" s="7" t="n">
-        <v>352.05</v>
+        <v>1350.5</v>
       </c>
       <c r="H66" s="8" t="n">
-        <v>1481.7616</v>
+        <v>1215.7143</v>
       </c>
       <c r="I66" s="7" t="n">
-        <v>352.05</v>
+        <v>1350.5</v>
       </c>
       <c r="J66" s="8" t="n">
-        <v>1481.7616</v>
+        <v>1215.7143</v>
       </c>
       <c r="K66" s="7" t="n">
-        <v>357.05</v>
+        <v>1328.4</v>
       </c>
       <c r="L66" s="8" t="n">
-        <v>1502.8063</v>
+        <v>1195.82</v>
       </c>
       <c r="M66" s="9" t="n">
-        <v>-1.4004</v>
+        <v>1.6637</v>
       </c>
       <c r="N66" s="10" t="n">
-        <v>-0.0272</v>
+        <v>0.02651</v>
       </c>
       <c r="O66" s="9" t="n">
-        <v>1.9421</v>
+        <v>1.5934</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>INE752E01010</t>
+          <t>INE059A01026</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Power Grid Corporation Of India Ltd.</t>
+          <t>Cipla Ltd.</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Pharmaceuticals &amp; Biotechnology</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -3463,103 +3403,73 @@
         </is>
       </c>
       <c r="F67" s="6" t="n">
-        <v>48981198</v>
+        <v>7766510</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>283.9</v>
+        <v>1440.1</v>
       </c>
       <c r="H67" s="8" t="n">
-        <v>1390.5762</v>
+        <v>1118.4551</v>
       </c>
       <c r="I67" s="7" t="n">
-        <v>283.9</v>
+        <v>1440.1</v>
       </c>
       <c r="J67" s="8" t="n">
-        <v>1390.5762</v>
+        <v>1118.4551</v>
       </c>
       <c r="K67" s="7" t="n">
-        <v>290.9</v>
+        <v>1437.9</v>
       </c>
       <c r="L67" s="8" t="n">
-        <v>1424.863</v>
+        <v>1116.7465</v>
       </c>
       <c r="M67" s="9" t="n">
-        <v>-2.4063</v>
+        <v>0.153</v>
       </c>
       <c r="N67" s="10" t="n">
-        <v>-0.04386</v>
+        <v>0.00224</v>
       </c>
       <c r="O67" s="9" t="n">
-        <v>1.8226</v>
+        <v>1.4659</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="n">
-        <v>46</v>
-      </c>
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>INE704J01044</t>
-        </is>
-      </c>
-      <c r="C68" s="5" t="inlineStr">
-        <is>
-          <t>Malco Energy Ltd.</t>
-        </is>
-      </c>
-      <c r="D68" s="5" t="inlineStr">
-        <is>
-          <t>Power</t>
-        </is>
-      </c>
-      <c r="E68" s="5" t="inlineStr">
-        <is>
-          <t>structural</t>
-        </is>
-      </c>
-      <c r="F68" s="6" t="n">
-        <v>341774084</v>
-      </c>
-      <c r="G68" s="7" t="n">
-        <v>33.35</v>
-      </c>
-      <c r="H68" s="8" t="n">
-        <v>1139.8166</v>
-      </c>
-      <c r="I68" s="7" t="n">
-        <v>33.35</v>
-      </c>
-      <c r="J68" s="8" t="n">
-        <v>1139.8166</v>
-      </c>
-      <c r="K68" s="7" t="n">
-        <v>34.45</v>
-      </c>
-      <c r="L68" s="8" t="n">
-        <v>1177.4117</v>
-      </c>
-      <c r="M68" s="9" t="n">
-        <v>-3.193</v>
-      </c>
-      <c r="N68" s="10" t="n">
-        <v>-0.0477</v>
-      </c>
-      <c r="O68" s="9" t="n">
-        <v>1.4939</v>
+      <c r="A68" s="11" t="n"/>
+      <c r="B68" s="11" t="n"/>
+      <c r="C68" s="12" t="inlineStr">
+        <is>
+          <t>Pharmaceuticals &amp; Biotechnology — subtotal</t>
+        </is>
+      </c>
+      <c r="D68" s="11" t="n"/>
+      <c r="E68" s="11" t="n"/>
+      <c r="F68" s="11" t="n"/>
+      <c r="G68" s="11" t="n"/>
+      <c r="H68" s="11" t="n"/>
+      <c r="I68" s="11" t="n"/>
+      <c r="J68" s="13" t="n">
+        <v>6948.016</v>
+      </c>
+      <c r="K68" s="11" t="n"/>
+      <c r="L68" s="11" t="n"/>
+      <c r="M68" s="11" t="n"/>
+      <c r="N68" s="11" t="n"/>
+      <c r="O68" s="14" t="n">
+        <v>9.109999999999999</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>INE694L01019</t>
+          <t>INE733E01010</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Talwandi Sabo Power Ltd.</t>
+          <t>NTPC Ltd.</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
@@ -3573,78 +3483,108 @@
         </is>
       </c>
       <c r="F69" s="6" t="n">
-        <v>268697918</v>
+        <v>51937485</v>
       </c>
       <c r="G69" s="7" t="n">
-        <v>42.42</v>
+        <v>352.05</v>
       </c>
       <c r="H69" s="8" t="n">
-        <v>1139.8166</v>
+        <v>1828.4592</v>
       </c>
       <c r="I69" s="7" t="n">
-        <v>42.42</v>
+        <v>352.05</v>
       </c>
       <c r="J69" s="8" t="n">
-        <v>1139.8166</v>
+        <v>1828.4592</v>
       </c>
       <c r="K69" s="7" t="n">
-        <v>43.61</v>
+        <v>357.05</v>
       </c>
       <c r="L69" s="8" t="n">
-        <v>1171.7916</v>
+        <v>1854.4279</v>
       </c>
       <c r="M69" s="9" t="n">
-        <v>-2.7287</v>
+        <v>-1.4004</v>
       </c>
       <c r="N69" s="10" t="n">
-        <v>-0.04076</v>
+        <v>-0.03356</v>
       </c>
       <c r="O69" s="9" t="n">
-        <v>1.4939</v>
+        <v>2.3965</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="11" t="n"/>
-      <c r="B70" s="11" t="n"/>
-      <c r="C70" s="12" t="inlineStr">
-        <is>
-          <t>Power — subtotal</t>
-        </is>
-      </c>
-      <c r="D70" s="11" t="n"/>
-      <c r="E70" s="11" t="n"/>
-      <c r="F70" s="11" t="n"/>
-      <c r="G70" s="11" t="n"/>
-      <c r="H70" s="11" t="n"/>
-      <c r="I70" s="11" t="n"/>
-      <c r="J70" s="13" t="n">
-        <v>5151.971</v>
-      </c>
-      <c r="K70" s="11" t="n"/>
-      <c r="L70" s="11" t="n"/>
-      <c r="M70" s="11" t="n"/>
-      <c r="N70" s="11" t="n"/>
-      <c r="O70" s="14" t="n">
-        <v>6.75</v>
+      <c r="A70" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>INE752E01010</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>Power Grid Corporation Of India Ltd.</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="n">
+        <v>53007141</v>
+      </c>
+      <c r="G70" s="7" t="n">
+        <v>283.9</v>
+      </c>
+      <c r="H70" s="8" t="n">
+        <v>1504.8727</v>
+      </c>
+      <c r="I70" s="7" t="n">
+        <v>283.9</v>
+      </c>
+      <c r="J70" s="8" t="n">
+        <v>1504.8727</v>
+      </c>
+      <c r="K70" s="7" t="n">
+        <v>290.9</v>
+      </c>
+      <c r="L70" s="8" t="n">
+        <v>1541.9777</v>
+      </c>
+      <c r="M70" s="9" t="n">
+        <v>-2.4063</v>
+      </c>
+      <c r="N70" s="10" t="n">
+        <v>-0.04746</v>
+      </c>
+      <c r="O70" s="9" t="n">
+        <v>1.9724</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>INE271C01023</t>
+          <t>INE704J01044</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>DLF Ltd.</t>
+          <t>Malco Energy Ltd.</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -3653,616 +3593,751 @@
         </is>
       </c>
       <c r="F71" s="6" t="n">
-        <v>18711079</v>
+        <v>347754213</v>
       </c>
       <c r="G71" s="7" t="n">
-        <v>621.35</v>
+        <v>33.35</v>
       </c>
       <c r="H71" s="8" t="n">
-        <v>1162.6129</v>
+        <v>1159.7603</v>
       </c>
       <c r="I71" s="7" t="n">
-        <v>621.35</v>
+        <v>33.35</v>
       </c>
       <c r="J71" s="8" t="n">
-        <v>1162.6129</v>
+        <v>1159.7603</v>
       </c>
       <c r="K71" s="7" t="n">
-        <v>618.15</v>
+        <v>34.45</v>
       </c>
       <c r="L71" s="8" t="n">
-        <v>1156.6253</v>
+        <v>1198.0133</v>
       </c>
       <c r="M71" s="9" t="n">
-        <v>0.5177</v>
+        <v>-3.193</v>
       </c>
       <c r="N71" s="10" t="n">
-        <v>0.007889999999999999</v>
+        <v>-0.04854</v>
       </c>
       <c r="O71" s="9" t="n">
-        <v>1.5238</v>
+        <v>1.5201</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="11" t="n"/>
-      <c r="B72" s="11" t="n"/>
-      <c r="C72" s="12" t="inlineStr">
-        <is>
-          <t>Realty — subtotal</t>
-        </is>
-      </c>
-      <c r="D72" s="11" t="n"/>
-      <c r="E72" s="11" t="n"/>
-      <c r="F72" s="11" t="n"/>
-      <c r="G72" s="11" t="n"/>
-      <c r="H72" s="11" t="n"/>
-      <c r="I72" s="11" t="n"/>
-      <c r="J72" s="13" t="n">
-        <v>1162.613</v>
-      </c>
-      <c r="K72" s="11" t="n"/>
-      <c r="L72" s="11" t="n"/>
-      <c r="M72" s="11" t="n"/>
-      <c r="N72" s="11" t="n"/>
-      <c r="O72" s="14" t="n">
-        <v>1.52</v>
+      <c r="A72" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>INE694L01019</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>Talwandi Sabo Power Ltd.</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="F72" s="6" t="n">
+        <v>273399411</v>
+      </c>
+      <c r="G72" s="7" t="n">
+        <v>42.42</v>
+      </c>
+      <c r="H72" s="8" t="n">
+        <v>1159.7603</v>
+      </c>
+      <c r="I72" s="7" t="n">
+        <v>42.42</v>
+      </c>
+      <c r="J72" s="8" t="n">
+        <v>1159.7603</v>
+      </c>
+      <c r="K72" s="7" t="n">
+        <v>43.61</v>
+      </c>
+      <c r="L72" s="8" t="n">
+        <v>1192.2948</v>
+      </c>
+      <c r="M72" s="9" t="n">
+        <v>-2.7287</v>
+      </c>
+      <c r="N72" s="10" t="n">
+        <v>-0.04148</v>
+      </c>
+      <c r="O72" s="9" t="n">
+        <v>1.5201</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>INE192R01011</t>
+          <t>INE848E01016</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>Avenue Supermarts Ltd.</t>
+          <t>NHPC Ltd.</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>structural</t>
+          <t>cyclical</t>
         </is>
       </c>
       <c r="F73" s="6" t="n">
-        <v>3450290</v>
+        <v>127312904</v>
       </c>
       <c r="G73" s="7" t="n">
-        <v>4294.6</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="H73" s="8" t="n">
-        <v>1481.7615</v>
+        <v>1010.8645</v>
       </c>
       <c r="I73" s="7" t="n">
-        <v>4294.6</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="J73" s="8" t="n">
-        <v>1481.7615</v>
+        <v>1010.8645</v>
       </c>
       <c r="K73" s="7" t="n">
-        <v>4336</v>
+        <v>79.31</v>
       </c>
       <c r="L73" s="8" t="n">
-        <v>1496.0457</v>
+        <v>1009.7186</v>
       </c>
       <c r="M73" s="9" t="n">
-        <v>-0.9548</v>
+        <v>0.1135</v>
       </c>
       <c r="N73" s="10" t="n">
-        <v>-0.01854</v>
+        <v>0.0015</v>
       </c>
       <c r="O73" s="9" t="n">
-        <v>1.9421</v>
+        <v>1.3249</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>INE849A01020</t>
+          <t>INE245A01021</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Trent Ltd.</t>
+          <t>Tata Power Company Ltd.</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Retailing</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>structural</t>
+          <t>cyclical</t>
         </is>
       </c>
       <c r="F74" s="6" t="n">
-        <v>4536301</v>
+        <v>25267900</v>
       </c>
       <c r="G74" s="7" t="n">
-        <v>3216.2</v>
+        <v>388.95</v>
       </c>
       <c r="H74" s="8" t="n">
-        <v>1458.9651</v>
+        <v>982.795</v>
       </c>
       <c r="I74" s="7" t="n">
-        <v>3216.2</v>
+        <v>388.95</v>
       </c>
       <c r="J74" s="8" t="n">
-        <v>1458.9651</v>
+        <v>982.795</v>
       </c>
       <c r="K74" s="7" t="n">
-        <v>3247</v>
+        <v>393.1</v>
       </c>
       <c r="L74" s="8" t="n">
-        <v>1472.9369</v>
+        <v>993.2811</v>
       </c>
       <c r="M74" s="9" t="n">
-        <v>-0.9486</v>
+        <v>-1.0557</v>
       </c>
       <c r="N74" s="10" t="n">
-        <v>-0.01814</v>
+        <v>-0.0136</v>
       </c>
       <c r="O74" s="9" t="n">
-        <v>1.9122</v>
+        <v>1.2881</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="5" t="n">
-        <v>51</v>
-      </c>
-      <c r="B75" s="5" t="inlineStr">
-        <is>
-          <t>INE758T01015</t>
-        </is>
-      </c>
-      <c r="C75" s="5" t="inlineStr">
-        <is>
-          <t>Eternal Ltd.</t>
-        </is>
-      </c>
-      <c r="D75" s="5" t="inlineStr">
-        <is>
-          <t>Retailing</t>
-        </is>
-      </c>
-      <c r="E75" s="5" t="inlineStr">
-        <is>
-          <t>structural</t>
-        </is>
-      </c>
-      <c r="F75" s="6" t="n">
-        <v>52713445</v>
-      </c>
-      <c r="G75" s="7" t="n">
-        <v>255.15</v>
-      </c>
-      <c r="H75" s="8" t="n">
-        <v>1344.9835</v>
-      </c>
-      <c r="I75" s="7" t="n">
-        <v>255.15</v>
-      </c>
-      <c r="J75" s="8" t="n">
-        <v>1344.9835</v>
-      </c>
-      <c r="K75" s="7" t="n">
-        <v>256.35</v>
-      </c>
-      <c r="L75" s="8" t="n">
-        <v>1351.3092</v>
-      </c>
-      <c r="M75" s="9" t="n">
-        <v>-0.4681</v>
-      </c>
-      <c r="N75" s="10" t="n">
-        <v>-0.00825</v>
-      </c>
-      <c r="O75" s="9" t="n">
-        <v>1.7628</v>
+      <c r="A75" s="11" t="n"/>
+      <c r="B75" s="11" t="n"/>
+      <c r="C75" s="12" t="inlineStr">
+        <is>
+          <t>Power — subtotal</t>
+        </is>
+      </c>
+      <c r="D75" s="11" t="n"/>
+      <c r="E75" s="11" t="n"/>
+      <c r="F75" s="11" t="n"/>
+      <c r="G75" s="11" t="n"/>
+      <c r="H75" s="11" t="n"/>
+      <c r="I75" s="11" t="n"/>
+      <c r="J75" s="13" t="n">
+        <v>7646.512</v>
+      </c>
+      <c r="K75" s="11" t="n"/>
+      <c r="L75" s="11" t="n"/>
+      <c r="M75" s="11" t="n"/>
+      <c r="N75" s="11" t="n"/>
+      <c r="O75" s="14" t="n">
+        <v>10.02</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>INE192R01011</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>Avenue Supermarts Ltd.</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>Retailing</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="n">
+        <v>3075155</v>
+      </c>
+      <c r="G76" s="7" t="n">
+        <v>4294.6</v>
+      </c>
+      <c r="H76" s="8" t="n">
+        <v>1320.6561</v>
+      </c>
+      <c r="I76" s="7" t="n">
+        <v>4294.6</v>
+      </c>
+      <c r="J76" s="8" t="n">
+        <v>1320.6561</v>
+      </c>
+      <c r="K76" s="7" t="n">
+        <v>4336</v>
+      </c>
+      <c r="L76" s="8" t="n">
+        <v>1333.3872</v>
+      </c>
+      <c r="M76" s="9" t="n">
+        <v>-0.9548</v>
+      </c>
+      <c r="N76" s="10" t="n">
+        <v>-0.01653</v>
+      </c>
+      <c r="O76" s="9" t="n">
+        <v>1.7309</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>INE849A01020</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>Trent Ltd.</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>Retailing</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>structural</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="n">
+        <v>3948273</v>
+      </c>
+      <c r="G77" s="7" t="n">
+        <v>3216.2</v>
+      </c>
+      <c r="H77" s="8" t="n">
+        <v>1269.8436</v>
+      </c>
+      <c r="I77" s="7" t="n">
+        <v>3216.2</v>
+      </c>
+      <c r="J77" s="8" t="n">
+        <v>1269.8436</v>
+      </c>
+      <c r="K77" s="7" t="n">
+        <v>3247</v>
+      </c>
+      <c r="L77" s="8" t="n">
+        <v>1282.0042</v>
+      </c>
+      <c r="M77" s="9" t="n">
+        <v>-0.9486</v>
+      </c>
+      <c r="N77" s="10" t="n">
+        <v>-0.01579</v>
+      </c>
+      <c r="O77" s="9" t="n">
+        <v>1.6643</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="11" t="n"/>
+      <c r="B78" s="11" t="n"/>
+      <c r="C78" s="12" t="inlineStr">
+        <is>
+          <t>Retailing — subtotal</t>
+        </is>
+      </c>
+      <c r="D78" s="11" t="n"/>
+      <c r="E78" s="11" t="n"/>
+      <c r="F78" s="11" t="n"/>
+      <c r="G78" s="11" t="n"/>
+      <c r="H78" s="11" t="n"/>
+      <c r="I78" s="11" t="n"/>
+      <c r="J78" s="13" t="n">
+        <v>2590.5</v>
+      </c>
+      <c r="K78" s="11" t="n"/>
+      <c r="L78" s="11" t="n"/>
+      <c r="M78" s="11" t="n"/>
+      <c r="N78" s="11" t="n"/>
+      <c r="O78" s="14" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="n">
         <v>52</v>
       </c>
-      <c r="B76" s="5" t="inlineStr">
-        <is>
-          <t>INE663F01032</t>
-        </is>
-      </c>
-      <c r="C76" s="5" t="inlineStr">
-        <is>
-          <t>Info Edge (India) Ltd.</t>
-        </is>
-      </c>
-      <c r="D76" s="5" t="inlineStr">
-        <is>
-          <t>Retailing</t>
-        </is>
-      </c>
-      <c r="E76" s="5" t="inlineStr">
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>INE397D01024</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>Bharti Airtel Ltd.</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>Telecom - Services</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
         <is>
           <t>structural</t>
         </is>
       </c>
-      <c r="F76" s="6" t="n">
-        <v>9781334</v>
-      </c>
-      <c r="G76" s="7" t="n">
-        <v>978.85</v>
-      </c>
-      <c r="H76" s="8" t="n">
-        <v>957.4459000000001</v>
-      </c>
-      <c r="I76" s="7" t="n">
-        <v>978.85</v>
-      </c>
-      <c r="J76" s="8" t="n">
-        <v>957.4459000000001</v>
-      </c>
-      <c r="K76" s="7" t="n">
-        <v>1009.8</v>
-      </c>
-      <c r="L76" s="8" t="n">
-        <v>987.7191</v>
-      </c>
-      <c r="M76" s="9" t="n">
-        <v>-3.065</v>
-      </c>
-      <c r="N76" s="10" t="n">
-        <v>-0.03846</v>
-      </c>
-      <c r="O76" s="9" t="n">
-        <v>1.2549</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="11" t="n"/>
-      <c r="B77" s="11" t="n"/>
-      <c r="C77" s="12" t="inlineStr">
-        <is>
-          <t>Retailing — subtotal</t>
-        </is>
-      </c>
-      <c r="D77" s="11" t="n"/>
-      <c r="E77" s="11" t="n"/>
-      <c r="F77" s="11" t="n"/>
-      <c r="G77" s="11" t="n"/>
-      <c r="H77" s="11" t="n"/>
-      <c r="I77" s="11" t="n"/>
-      <c r="J77" s="13" t="n">
-        <v>5243.156</v>
-      </c>
-      <c r="K77" s="11" t="n"/>
-      <c r="L77" s="11" t="n"/>
-      <c r="M77" s="11" t="n"/>
-      <c r="N77" s="11" t="n"/>
-      <c r="O77" s="14" t="n">
-        <v>6.87</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="5" t="n">
+      <c r="F79" s="6" t="n">
+        <v>5576244</v>
+      </c>
+      <c r="G79" s="7" t="n">
+        <v>1850.7</v>
+      </c>
+      <c r="H79" s="8" t="n">
+        <v>1031.9955</v>
+      </c>
+      <c r="I79" s="7" t="n">
+        <v>1850.7</v>
+      </c>
+      <c r="J79" s="8" t="n">
+        <v>1031.9955</v>
+      </c>
+      <c r="K79" s="7" t="n">
+        <v>1877.3</v>
+      </c>
+      <c r="L79" s="8" t="n">
+        <v>1046.8283</v>
+      </c>
+      <c r="M79" s="9" t="n">
+        <v>-1.4169</v>
+      </c>
+      <c r="N79" s="10" t="n">
+        <v>-0.01916</v>
+      </c>
+      <c r="O79" s="9" t="n">
+        <v>1.3526</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="11" t="n"/>
+      <c r="B80" s="11" t="n"/>
+      <c r="C80" s="12" t="inlineStr">
+        <is>
+          <t>Telecom - Services — subtotal</t>
+        </is>
+      </c>
+      <c r="D80" s="11" t="n"/>
+      <c r="E80" s="11" t="n"/>
+      <c r="F80" s="11" t="n"/>
+      <c r="G80" s="11" t="n"/>
+      <c r="H80" s="11" t="n"/>
+      <c r="I80" s="11" t="n"/>
+      <c r="J80" s="13" t="n">
+        <v>1031.995</v>
+      </c>
+      <c r="K80" s="11" t="n"/>
+      <c r="L80" s="11" t="n"/>
+      <c r="M80" s="11" t="n"/>
+      <c r="N80" s="11" t="n"/>
+      <c r="O80" s="14" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="B78" s="5" t="inlineStr">
-        <is>
-          <t>INE397D01024</t>
-        </is>
-      </c>
-      <c r="C78" s="5" t="inlineStr">
-        <is>
-          <t>Bharti Airtel Ltd.</t>
-        </is>
-      </c>
-      <c r="D78" s="5" t="inlineStr">
-        <is>
-          <t>Telecom - Services</t>
-        </is>
-      </c>
-      <c r="E78" s="5" t="inlineStr">
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>INE761H01022</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>Page Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>Textiles &amp; Apparels</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
         <is>
           <t>structural</t>
         </is>
       </c>
-      <c r="F78" s="6" t="n">
-        <v>7390608</v>
-      </c>
-      <c r="G78" s="7" t="n">
-        <v>1850.7</v>
-      </c>
-      <c r="H78" s="8" t="n">
-        <v>1367.7798</v>
-      </c>
-      <c r="I78" s="7" t="n">
-        <v>1850.7</v>
-      </c>
-      <c r="J78" s="8" t="n">
-        <v>1367.7798</v>
-      </c>
-      <c r="K78" s="7" t="n">
-        <v>1877.3</v>
-      </c>
-      <c r="L78" s="8" t="n">
-        <v>1387.4388</v>
-      </c>
-      <c r="M78" s="9" t="n">
-        <v>-1.4169</v>
-      </c>
-      <c r="N78" s="10" t="n">
-        <v>-0.0254</v>
-      </c>
-      <c r="O78" s="9" t="n">
-        <v>1.7927</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="11" t="n"/>
-      <c r="B79" s="11" t="n"/>
-      <c r="C79" s="12" t="inlineStr">
-        <is>
-          <t>Telecom - Services — subtotal</t>
-        </is>
-      </c>
-      <c r="D79" s="11" t="n"/>
-      <c r="E79" s="11" t="n"/>
-      <c r="F79" s="11" t="n"/>
-      <c r="G79" s="11" t="n"/>
-      <c r="H79" s="11" t="n"/>
-      <c r="I79" s="11" t="n"/>
-      <c r="J79" s="13" t="n">
-        <v>1367.78</v>
-      </c>
-      <c r="K79" s="11" t="n"/>
-      <c r="L79" s="11" t="n"/>
-      <c r="M79" s="11" t="n"/>
-      <c r="N79" s="11" t="n"/>
-      <c r="O79" s="14" t="n">
-        <v>1.79</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="5" t="n">
+      <c r="F81" s="6" t="n">
+        <v>317186</v>
+      </c>
+      <c r="G81" s="7" t="n">
+        <v>40950</v>
+      </c>
+      <c r="H81" s="8" t="n">
+        <v>1298.8767</v>
+      </c>
+      <c r="I81" s="7" t="n">
+        <v>40950</v>
+      </c>
+      <c r="J81" s="8" t="n">
+        <v>1298.8767</v>
+      </c>
+      <c r="K81" s="7" t="n">
+        <v>40885</v>
+      </c>
+      <c r="L81" s="8" t="n">
+        <v>1296.815</v>
+      </c>
+      <c r="M81" s="9" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="N81" s="10" t="n">
+        <v>0.00271</v>
+      </c>
+      <c r="O81" s="9" t="n">
+        <v>1.7024</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="11" t="n"/>
+      <c r="B82" s="11" t="n"/>
+      <c r="C82" s="12" t="inlineStr">
+        <is>
+          <t>Textiles &amp; Apparels — subtotal</t>
+        </is>
+      </c>
+      <c r="D82" s="11" t="n"/>
+      <c r="E82" s="11" t="n"/>
+      <c r="F82" s="11" t="n"/>
+      <c r="G82" s="11" t="n"/>
+      <c r="H82" s="11" t="n"/>
+      <c r="I82" s="11" t="n"/>
+      <c r="J82" s="13" t="n">
+        <v>1298.877</v>
+      </c>
+      <c r="K82" s="11" t="n"/>
+      <c r="L82" s="11" t="n"/>
+      <c r="M82" s="11" t="n"/>
+      <c r="N82" s="11" t="n"/>
+      <c r="O82" s="14" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="n">
         <v>54</v>
       </c>
-      <c r="B80" s="5" t="inlineStr">
-        <is>
-          <t>INE761H01022</t>
-        </is>
-      </c>
-      <c r="C80" s="5" t="inlineStr">
-        <is>
-          <t>Page Industries Ltd.</t>
-        </is>
-      </c>
-      <c r="D80" s="5" t="inlineStr">
-        <is>
-          <t>Textiles &amp; Apparels</t>
-        </is>
-      </c>
-      <c r="E80" s="5" t="inlineStr">
-        <is>
-          <t>structural</t>
-        </is>
-      </c>
-      <c r="F80" s="6" t="n">
-        <v>317312</v>
-      </c>
-      <c r="G80" s="7" t="n">
-        <v>40950</v>
-      </c>
-      <c r="H80" s="8" t="n">
-        <v>1299.3926</v>
-      </c>
-      <c r="I80" s="7" t="n">
-        <v>40950</v>
-      </c>
-      <c r="J80" s="8" t="n">
-        <v>1299.3926</v>
-      </c>
-      <c r="K80" s="7" t="n">
-        <v>40885</v>
-      </c>
-      <c r="L80" s="8" t="n">
-        <v>1297.3301</v>
-      </c>
-      <c r="M80" s="9" t="n">
-        <v>0.159</v>
-      </c>
-      <c r="N80" s="10" t="n">
-        <v>0.00271</v>
-      </c>
-      <c r="O80" s="9" t="n">
-        <v>1.7031</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="11" t="n"/>
-      <c r="B81" s="11" t="n"/>
-      <c r="C81" s="12" t="inlineStr">
-        <is>
-          <t>Textiles &amp; Apparels — subtotal</t>
-        </is>
-      </c>
-      <c r="D81" s="11" t="n"/>
-      <c r="E81" s="11" t="n"/>
-      <c r="F81" s="11" t="n"/>
-      <c r="G81" s="11" t="n"/>
-      <c r="H81" s="11" t="n"/>
-      <c r="I81" s="11" t="n"/>
-      <c r="J81" s="13" t="n">
-        <v>1299.393</v>
-      </c>
-      <c r="K81" s="11" t="n"/>
-      <c r="L81" s="11" t="n"/>
-      <c r="M81" s="11" t="n"/>
-      <c r="N81" s="11" t="n"/>
-      <c r="O81" s="14" t="n">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="n">
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>INE517F01014</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>Gujarat Pipavav Port Ltd.</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>Transport Infrastructure</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>tactical</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="n">
+        <v>25107051</v>
+      </c>
+      <c r="G83" s="7" t="n">
+        <v>153.81</v>
+      </c>
+      <c r="H83" s="8" t="n">
+        <v>386.1716</v>
+      </c>
+      <c r="I83" s="7" t="n">
+        <v>153.81</v>
+      </c>
+      <c r="J83" s="8" t="n">
+        <v>386.1716</v>
+      </c>
+      <c r="K83" s="7" t="n">
+        <v>156.26</v>
+      </c>
+      <c r="L83" s="8" t="n">
+        <v>392.3228</v>
+      </c>
+      <c r="M83" s="9" t="n">
+        <v>-1.5679</v>
+      </c>
+      <c r="N83" s="10" t="n">
+        <v>-0.007939999999999999</v>
+      </c>
+      <c r="O83" s="9" t="n">
+        <v>0.5061</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="11" t="n"/>
+      <c r="B84" s="11" t="n"/>
+      <c r="C84" s="12" t="inlineStr">
+        <is>
+          <t>Transport Infrastructure — subtotal</t>
+        </is>
+      </c>
+      <c r="D84" s="11" t="n"/>
+      <c r="E84" s="11" t="n"/>
+      <c r="F84" s="11" t="n"/>
+      <c r="G84" s="11" t="n"/>
+      <c r="H84" s="11" t="n"/>
+      <c r="I84" s="11" t="n"/>
+      <c r="J84" s="13" t="n">
+        <v>386.172</v>
+      </c>
+      <c r="K84" s="11" t="n"/>
+      <c r="L84" s="11" t="n"/>
+      <c r="M84" s="11" t="n"/>
+      <c r="N84" s="11" t="n"/>
+      <c r="O84" s="14" t="n">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="n">
         <v>55</v>
       </c>
-      <c r="B82" s="5" t="inlineStr">
-        <is>
-          <t>INE517F01014</t>
-        </is>
-      </c>
-      <c r="C82" s="5" t="inlineStr">
-        <is>
-          <t>Gujarat Pipavav Port Ltd.</t>
-        </is>
-      </c>
-      <c r="D82" s="5" t="inlineStr">
-        <is>
-          <t>Transport Infrastructure</t>
-        </is>
-      </c>
-      <c r="E82" s="5" t="inlineStr">
-        <is>
-          <t>tactical</t>
-        </is>
-      </c>
-      <c r="F82" s="6" t="n">
-        <v>25107051</v>
-      </c>
-      <c r="G82" s="7" t="n">
-        <v>153.81</v>
-      </c>
-      <c r="H82" s="8" t="n">
-        <v>386.1716</v>
-      </c>
-      <c r="I82" s="7" t="n">
-        <v>153.81</v>
-      </c>
-      <c r="J82" s="8" t="n">
-        <v>386.1716</v>
-      </c>
-      <c r="K82" s="7" t="n">
-        <v>156.26</v>
-      </c>
-      <c r="L82" s="8" t="n">
-        <v>392.3228</v>
-      </c>
-      <c r="M82" s="9" t="n">
-        <v>-1.5679</v>
-      </c>
-      <c r="N82" s="10" t="n">
-        <v>-0.007939999999999999</v>
-      </c>
-      <c r="O82" s="9" t="n">
-        <v>0.5061</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="11" t="n"/>
-      <c r="B83" s="11" t="n"/>
-      <c r="C83" s="12" t="inlineStr">
-        <is>
-          <t>Transport Infrastructure — subtotal</t>
-        </is>
-      </c>
-      <c r="D83" s="11" t="n"/>
-      <c r="E83" s="11" t="n"/>
-      <c r="F83" s="11" t="n"/>
-      <c r="G83" s="11" t="n"/>
-      <c r="H83" s="11" t="n"/>
-      <c r="I83" s="11" t="n"/>
-      <c r="J83" s="13" t="n">
-        <v>386.172</v>
-      </c>
-      <c r="K83" s="11" t="n"/>
-      <c r="L83" s="11" t="n"/>
-      <c r="M83" s="11" t="n"/>
-      <c r="N83" s="11" t="n"/>
-      <c r="O83" s="14" t="n">
-        <v>0.51</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>EQUITY</t>
-        </is>
-      </c>
-      <c r="C85" s="15" t="n">
-        <v>72482.151</v>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>₹cr</t>
-        </is>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>INE111A01025</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>Container Corporation Of India Ltd.</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>Transport Services</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>cyclical</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="n">
+        <v>21487686</v>
+      </c>
+      <c r="G85" s="7" t="n">
+        <v>469.8</v>
+      </c>
+      <c r="H85" s="8" t="n">
+        <v>1009.4915</v>
+      </c>
+      <c r="I85" s="7" t="n">
+        <v>469.8</v>
+      </c>
+      <c r="J85" s="8" t="n">
+        <v>1009.4915</v>
+      </c>
+      <c r="K85" s="7" t="n">
+        <v>473.95</v>
+      </c>
+      <c r="L85" s="8" t="n">
+        <v>1018.4089</v>
+      </c>
+      <c r="M85" s="9" t="n">
+        <v>-0.8756</v>
+      </c>
+      <c r="N85" s="10" t="n">
+        <v>-0.01159</v>
+      </c>
+      <c r="O85" s="9" t="n">
+        <v>1.3231</v>
       </c>
     </row>
     <row r="86">
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>CASH</t>
-        </is>
-      </c>
-      <c r="C86" s="15" t="n">
-        <v>3814.849</v>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>₹cr (5.0%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>TOTAL (NAV base)</t>
-        </is>
-      </c>
-      <c r="C87" s="15" t="n">
-        <v>76297</v>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>₹cr</t>
-        </is>
+      <c r="A86" s="11" t="n"/>
+      <c r="B86" s="11" t="n"/>
+      <c r="C86" s="12" t="inlineStr">
+        <is>
+          <t>Transport Services — subtotal</t>
+        </is>
+      </c>
+      <c r="D86" s="11" t="n"/>
+      <c r="E86" s="11" t="n"/>
+      <c r="F86" s="11" t="n"/>
+      <c r="G86" s="11" t="n"/>
+      <c r="H86" s="11" t="n"/>
+      <c r="I86" s="11" t="n"/>
+      <c r="J86" s="13" t="n">
+        <v>1009.491</v>
+      </c>
+      <c r="K86" s="11" t="n"/>
+      <c r="L86" s="11" t="n"/>
+      <c r="M86" s="11" t="n"/>
+      <c r="N86" s="11" t="n"/>
+      <c r="O86" s="14" t="n">
+        <v>1.32</v>
       </c>
     </row>
     <row r="88">
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>HOLDINGS</t>
+          <t>EQUITY</t>
         </is>
       </c>
       <c r="C88" s="15" t="n">
-        <v>55</v>
+        <v>72482.151</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>names</t>
+          <t>₹cr</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="B89" s="2" t="inlineStr">
         <is>
+          <t>CASH</t>
+        </is>
+      </c>
+      <c r="C89" s="15" t="n">
+        <v>3814.849</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>₹cr (5.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>TOTAL (NAV base)</t>
+        </is>
+      </c>
+      <c r="C90" s="15" t="n">
+        <v>76297</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>₹cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>HOLDINGS</t>
+        </is>
+      </c>
+      <c r="C91" s="15" t="n">
+        <v>55</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>names</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>DAY RETURN</t>
         </is>
       </c>
-      <c r="C89" s="15" t="n">
-        <v>-0.5324</v>
-      </c>
-      <c r="D89" t="inlineStr">
+      <c r="C92" s="15" t="n">
+        <v>-0.4713</v>
+      </c>
+      <c r="D92" t="inlineStr">
         <is>
           <t>%</t>
         </is>
